--- a/database/ML_ScaleUp_v02.xlsx
+++ b/database/ML_ScaleUp_v02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\S2501 ECM Generator\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E447D8-5F17-4BE4-8813-620812812478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B5171E-9FD3-4774-A19F-059900D8556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
   </bookViews>
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2351" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="1171">
   <si>
     <t>City</t>
   </si>
@@ -3779,6 +3779,192 @@
   </si>
   <si>
     <t>ML_EP</t>
+  </si>
+  <si>
+    <t>Wall-Name</t>
+  </si>
+  <si>
+    <t>SBB230</t>
+  </si>
+  <si>
+    <t>SBB230_XPS_5</t>
+  </si>
+  <si>
+    <t>SBB230_XPS_10</t>
+  </si>
+  <si>
+    <t>SBB230_XPS_25</t>
+  </si>
+  <si>
+    <t>SBB230_XPS_50</t>
+  </si>
+  <si>
+    <t>ACC200</t>
+  </si>
+  <si>
+    <t>ACC200_EPS_25</t>
+  </si>
+  <si>
+    <t>ACC200_EPS_50</t>
+  </si>
+  <si>
+    <t>ACC200_PUF_50</t>
+  </si>
+  <si>
+    <t>FAB230_PUF_25</t>
+  </si>
+  <si>
+    <t>FAB230_PUF_50</t>
+  </si>
+  <si>
+    <t>SCB200</t>
+  </si>
+  <si>
+    <t>SCB200_XPS_5</t>
+  </si>
+  <si>
+    <t>SCB200_EPS_15</t>
+  </si>
+  <si>
+    <t>SCB200_EPS_20</t>
+  </si>
+  <si>
+    <t>SCB200_XPS_25</t>
+  </si>
+  <si>
+    <t>SCB200_XPS_50</t>
+  </si>
+  <si>
+    <t>SCB200_EPS_25</t>
+  </si>
+  <si>
+    <t>SCB200_EPS_50</t>
+  </si>
+  <si>
+    <t>RC200</t>
+  </si>
+  <si>
+    <t>Roof-Name</t>
+  </si>
+  <si>
+    <t>ML_RC200_XPS25</t>
+  </si>
+  <si>
+    <t>ML_RC200_XPS50</t>
+  </si>
+  <si>
+    <t>RC200_XPS25</t>
+  </si>
+  <si>
+    <t>RC200_XPS50</t>
+  </si>
+  <si>
+    <t>ML_RC200_XPS75</t>
+  </si>
+  <si>
+    <t>ML_RC200_XPS100</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF25</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF50</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF75</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF100</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS2.5</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS5</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS7.5</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS10</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS12.5</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS15</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS17.5</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS20</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS25</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS50</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS75</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS100</t>
+  </si>
+  <si>
+    <t>RC200_XPS75</t>
+  </si>
+  <si>
+    <t>RC200_XPS100</t>
+  </si>
+  <si>
+    <t>RC200_PUF25</t>
+  </si>
+  <si>
+    <t>RC200_PUF50</t>
+  </si>
+  <si>
+    <t>RC200_PUF75</t>
+  </si>
+  <si>
+    <t>RC200_PUF100</t>
+  </si>
+  <si>
+    <t>RC200_EPS2.5</t>
+  </si>
+  <si>
+    <t>RC200_EPS5</t>
+  </si>
+  <si>
+    <t>RC200_EPS7.5</t>
+  </si>
+  <si>
+    <t>RC200_EPS10</t>
+  </si>
+  <si>
+    <t>RC200_EPS12.5</t>
+  </si>
+  <si>
+    <t>RC200_EPS15</t>
+  </si>
+  <si>
+    <t>RC200_EPS17.5</t>
+  </si>
+  <si>
+    <t>RC200_EPS20</t>
+  </si>
+  <si>
+    <t>RC200_EPS25</t>
+  </si>
+  <si>
+    <t>RC200_EPS50</t>
+  </si>
+  <si>
+    <t>RC200_EPS75</t>
+  </si>
+  <si>
+    <t>RC200_EPS100</t>
   </si>
 </sst>
 </file>
@@ -9407,23 +9593,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229818EF-9CDD-4D5B-ADA4-8AF24F6E0710}">
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="33" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="34" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>963</v>
       </c>
@@ -9431,103 +9618,106 @@
         <v>964</v>
       </c>
       <c r="C1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D1" t="s">
         <v>965</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>966</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>967</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>968</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>969</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>970</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>971</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>972</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>973</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>974</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>975</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>976</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>977</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>978</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>979</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>980</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>981</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>982</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>983</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>984</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>985</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>986</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>987</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>988</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>989</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>990</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>991</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>992</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>993</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>994</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>995</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>997</v>
       </c>
@@ -9535,73 +9725,76 @@
         <v>998</v>
       </c>
       <c r="C2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D2" t="s">
         <v>999</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1000</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>1001</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>1000</v>
       </c>
-      <c r="J2" s="17">
+      <c r="K2" s="17">
         <f>CONVERT(15,"mm","ft")</f>
         <v>4.9212598425196853E-2</v>
       </c>
-      <c r="K2" s="17">
+      <c r="L2" s="17">
         <f>CONVERT(230,"mm","ft")</f>
         <v>0.75459317585301833</v>
       </c>
-      <c r="L2" s="17">
+      <c r="M2" s="17">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P2" s="4">
+      <c r="Q2" s="4">
         <f>0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="R2" s="4">
         <f>0.98*5.678263243</f>
         <v>5.5646979781399999</v>
       </c>
-      <c r="R2" s="4">
+      <c r="S2" s="4">
         <f>0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="V2" s="4">
+      <c r="W2" s="4">
         <f>1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="W2" s="4">
+      <c r="X2" s="4">
         <f>1920*0.062427961</f>
         <v>119.86168511999999</v>
       </c>
-      <c r="X2" s="4">
+      <c r="Y2" s="4">
         <f>1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>997</v>
       </c>
-      <c r="AB2" s="4">
+      <c r="AC2" s="4">
         <f>840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AC2" s="18">
+      <c r="AD2" s="18">
         <f>800* 0.000239005736</f>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AD2" s="4">
+      <c r="AE2" s="4">
         <f>840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1002</v>
       </c>
@@ -9609,73 +9802,76 @@
         <v>1003</v>
       </c>
       <c r="C3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D3" t="s">
         <v>1004</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>1000</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1005</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>1001</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <f>CONVERT(10,"mm","ft")</f>
         <v>3.2808398950131233E-2</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="4">
         <f>CONVERT(230,"mm","ft")</f>
         <v>0.75459317585301833</v>
       </c>
-      <c r="P3" s="4">
-        <f t="shared" ref="P3:P21" si="0">0.72*5.678263243</f>
+      <c r="Q3" s="4">
+        <f t="shared" ref="Q3:Q21" si="0">0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="R3" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <f>0.98*5.678263243</f>
         <v>5.5646979781399999</v>
       </c>
-      <c r="V3" s="4">
-        <f t="shared" ref="V3:V21" si="1">1762*0.062427961</f>
+      <c r="W3" s="4">
+        <f t="shared" ref="W3:W21" si="1">1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="W3" s="20">
+      <c r="X3" s="20">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="X3" s="4">
+      <c r="Y3" s="4">
         <f>1920*0.062427961</f>
         <v>119.86168511999999</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>1002</v>
       </c>
-      <c r="AB3" s="4">
-        <f t="shared" ref="AB3:AB21" si="2">840* 0.000239005736</f>
+      <c r="AC3" s="4">
+        <f t="shared" ref="AC3:AC21" si="2">840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AC3" s="18">
+      <c r="AD3" s="18">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD3" s="4">
+      <c r="AE3" s="4">
         <f>800* 0.000239005736</f>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1006</v>
       </c>
@@ -9683,73 +9879,76 @@
         <v>1007</v>
       </c>
       <c r="C4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D4" t="s">
         <v>1008</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>1000</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>1005</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>1001</v>
       </c>
-      <c r="J4" s="4">
-        <f t="shared" ref="J4:J21" si="3">CONVERT(20,"mm","ft")</f>
+      <c r="K4" s="4">
+        <f t="shared" ref="K4:K21" si="3">CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <f>CONVERT(10,"mm","ft")</f>
         <v>3.2808398950131233E-2</v>
       </c>
-      <c r="L4" s="4">
-        <f t="shared" ref="L4:L12" si="4">CONVERT(230,"mm","ft")</f>
+      <c r="M4" s="4">
+        <f t="shared" ref="M4:M12" si="4">CONVERT(230,"mm","ft")</f>
         <v>0.75459317585301833</v>
       </c>
-      <c r="P4" s="4">
+      <c r="Q4" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q4" s="4">
-        <f t="shared" ref="Q4:Q5" si="5">0.03*5.678263243</f>
+      <c r="R4" s="4">
+        <f t="shared" ref="R4:R5" si="5">0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R4" s="4">
-        <f t="shared" ref="R4:R14" si="6">0.98*5.678263243</f>
+      <c r="S4" s="4">
+        <f t="shared" ref="S4:S14" si="6">0.98*5.678263243</f>
         <v>5.5646979781399999</v>
       </c>
-      <c r="V4" s="4">
+      <c r="W4" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W4" s="20">
-        <f t="shared" ref="W4" si="7">35*0.062427961</f>
+      <c r="X4" s="20">
+        <f t="shared" ref="X4" si="7">35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="X4" s="4">
-        <f t="shared" ref="X4:X6" si="8">1920*0.062427961</f>
+      <c r="Y4" s="4">
+        <f t="shared" ref="Y4:Y6" si="8">1920*0.062427961</f>
         <v>119.86168511999999</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>1006</v>
       </c>
-      <c r="AB4" s="4">
+      <c r="AC4" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC4" s="18">
-        <f t="shared" ref="AC4:AC6" si="9">1213* 0.000239005736</f>
+      <c r="AD4" s="18">
+        <f t="shared" ref="AD4:AD6" si="9">1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD4" s="4">
-        <f t="shared" ref="AD4:AD6" si="10">800* 0.000239005736</f>
+      <c r="AE4" s="4">
+        <f t="shared" ref="AE4:AE6" si="10">800* 0.000239005736</f>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1009</v>
       </c>
@@ -9757,73 +9956,76 @@
         <v>1010</v>
       </c>
       <c r="C5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D5" t="s">
         <v>1011</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>1000</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>1012</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>1001</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <f t="shared" si="4"/>
         <v>0.75459317585301833</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="R5" s="4">
         <f t="shared" si="5"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <f t="shared" si="6"/>
         <v>5.5646979781399999</v>
       </c>
-      <c r="V5" s="4">
+      <c r="W5" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W5" s="20">
+      <c r="X5" s="20">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X5" s="4">
+      <c r="Y5" s="4">
         <f t="shared" si="8"/>
         <v>119.86168511999999</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>1009</v>
       </c>
-      <c r="AB5" s="4">
+      <c r="AC5" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC5" s="18">
+      <c r="AD5" s="18">
         <f t="shared" si="9"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AD5" s="4">
+      <c r="AE5" s="4">
         <f t="shared" si="10"/>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1013</v>
       </c>
@@ -9831,73 +10033,76 @@
         <v>1014</v>
       </c>
       <c r="C6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D6" t="s">
         <v>1015</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>1000</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>1012</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>1001</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <f t="shared" si="4"/>
         <v>0.75459317585301833</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="R6" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <f t="shared" si="6"/>
         <v>5.5646979781399999</v>
       </c>
-      <c r="V6" s="4">
+      <c r="W6" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W6" s="20">
+      <c r="X6" s="20">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X6" s="4">
+      <c r="Y6" s="4">
         <f t="shared" si="8"/>
         <v>119.86168511999999</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>1013</v>
       </c>
-      <c r="AB6" s="4">
+      <c r="AC6" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC6" s="18">
+      <c r="AD6" s="18">
         <f t="shared" si="9"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AD6" s="4">
+      <c r="AE6" s="4">
         <f t="shared" si="10"/>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1016</v>
       </c>
@@ -9905,73 +10110,76 @@
         <v>1017</v>
       </c>
       <c r="C7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D7" t="s">
         <v>1018</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>1000</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1019</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>1000</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <f>CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P7" s="4">
+      <c r="Q7" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="R7" s="4">
         <f>0.18*5.678263243</f>
         <v>1.02208738374</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <f>0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="V7" s="4">
+      <c r="W7" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W7" s="20">
+      <c r="X7" s="20">
         <f>642*0.062427961</f>
         <v>40.078750962000001</v>
       </c>
-      <c r="X7" s="4">
+      <c r="Y7" s="4">
         <f>1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>1016</v>
       </c>
-      <c r="AB7" s="4">
+      <c r="AC7" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC7" s="18">
+      <c r="AD7" s="18">
         <f>1240* 0.000239005736</f>
         <v>0.29636711263999999</v>
       </c>
-      <c r="AD7" s="4">
+      <c r="AE7" s="4">
         <f>840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1020</v>
       </c>
@@ -9979,73 +10187,76 @@
         <v>1021</v>
       </c>
       <c r="C8" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D8" t="s">
         <v>1022</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>1000</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>1012</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>1019</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <f>CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P8" s="4">
+      <c r="Q8" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <f>0.18*5.678263243</f>
         <v>1.02208738374</v>
       </c>
-      <c r="V8" s="4">
+      <c r="W8" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W8" s="20">
-        <f t="shared" ref="W8:W9" si="11">28*0.062427961</f>
+      <c r="X8" s="20">
+        <f t="shared" ref="X8:X9" si="11">28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X8" s="4">
+      <c r="Y8" s="4">
         <f>642*0.062427961</f>
         <v>40.078750962000001</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>1020</v>
       </c>
-      <c r="AB8" s="4">
+      <c r="AC8" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC8" s="18">
+      <c r="AD8" s="18">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD8" s="4">
+      <c r="AE8" s="4">
         <f>1240* 0.000239005736</f>
         <v>0.29636711263999999</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1023</v>
       </c>
@@ -10053,73 +10264,76 @@
         <v>1024</v>
       </c>
       <c r="C9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D9" t="s">
         <v>1025</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>1000</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>1012</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>1019</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="L9" s="4">
-        <f t="shared" ref="L9:L10" si="12">CONVERT(200,"mm","ft")</f>
+      <c r="M9" s="4">
+        <f t="shared" ref="M9:M10" si="12">CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P9" s="4">
+      <c r="Q9" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q9" s="4">
-        <f t="shared" ref="Q9" si="13">0.04*5.678263243</f>
+      <c r="R9" s="4">
+        <f t="shared" ref="R9" si="13">0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <f>0.18*5.678263243</f>
         <v>1.02208738374</v>
       </c>
-      <c r="V9" s="4">
+      <c r="W9" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W9" s="20">
+      <c r="X9" s="20">
         <f t="shared" si="11"/>
         <v>1.747982908</v>
       </c>
-      <c r="X9" s="4">
+      <c r="Y9" s="4">
         <f>642*0.062427961</f>
         <v>40.078750962000001</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>1023</v>
       </c>
-      <c r="AB9" s="4">
+      <c r="AC9" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC9" s="18">
+      <c r="AD9" s="18">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD9" s="4">
+      <c r="AE9" s="4">
         <f>1240* 0.000239005736</f>
         <v>0.29636711263999999</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1026</v>
       </c>
@@ -10127,73 +10341,76 @@
         <v>1027</v>
       </c>
       <c r="C10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D10" t="s">
         <v>1028</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>1000</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>1029</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>1019</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <f t="shared" si="12"/>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P10" s="4">
+      <c r="Q10" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="R10" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <f>0.18*5.678263243</f>
         <v>1.02208738374</v>
       </c>
-      <c r="V10" s="4">
+      <c r="W10" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W10" s="20">
+      <c r="X10" s="20">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
-      <c r="X10" s="4">
+      <c r="Y10" s="4">
         <f>642*0.062427961</f>
         <v>40.078750962000001</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>1026</v>
       </c>
-      <c r="AB10" s="4">
+      <c r="AC10" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC10" s="18">
+      <c r="AD10" s="18">
         <f>1590* 0.000239005736</f>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AD10" s="4">
+      <c r="AE10" s="4">
         <f>1240* 0.000239005736</f>
         <v>0.29636711263999999</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1030</v>
       </c>
@@ -10201,73 +10418,76 @@
         <v>1031</v>
       </c>
       <c r="C11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D11" t="s">
         <v>1032</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>1000</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>1029</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>1033</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
         <f t="shared" si="4"/>
         <v>0.75459317585301833</v>
       </c>
-      <c r="P11" s="4">
+      <c r="Q11" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="R11" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <f>0.86*5.678263243</f>
         <v>4.8833063889799995</v>
       </c>
-      <c r="V11" s="4">
+      <c r="W11" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W11" s="20">
+      <c r="X11" s="20">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
-      <c r="X11" s="4">
+      <c r="Y11" s="4">
         <f>1650*0.062427961</f>
         <v>103.00613564999999</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>1030</v>
       </c>
-      <c r="AB11" s="4">
+      <c r="AC11" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC11" s="18">
+      <c r="AD11" s="18">
         <f>1590* 0.000239005736</f>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AD11" s="4">
+      <c r="AE11" s="4">
         <f>930* 0.000239005736</f>
         <v>0.22227533448</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1034</v>
       </c>
@@ -10275,73 +10495,76 @@
         <v>1035</v>
       </c>
       <c r="C12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D12" t="s">
         <v>1036</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>1000</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>1029</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>1033</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K12" s="4">
+      <c r="L12" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
         <f t="shared" si="4"/>
         <v>0.75459317585301833</v>
       </c>
-      <c r="P12" s="4">
+      <c r="Q12" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="R12" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R12" s="4">
+      <c r="S12" s="4">
         <f>0.86*5.678263243</f>
         <v>4.8833063889799995</v>
       </c>
-      <c r="V12" s="4">
+      <c r="W12" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W12" s="20">
+      <c r="X12" s="20">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
-      <c r="X12" s="4">
+      <c r="Y12" s="4">
         <f>1650*0.062427961</f>
         <v>103.00613564999999</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>1034</v>
       </c>
-      <c r="AB12" s="4">
+      <c r="AC12" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC12" s="18">
+      <c r="AD12" s="18">
         <f>1590* 0.000239005736</f>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AD12" s="4">
+      <c r="AE12" s="4">
         <f>930* 0.000239005736</f>
         <v>0.22227533448</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1037</v>
       </c>
@@ -10349,73 +10572,76 @@
         <v>1038</v>
       </c>
       <c r="C13" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D13" t="s">
         <v>1039</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1000</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1040</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>1000</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K13" s="4">
+      <c r="L13" s="4">
         <f>CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P13" s="4">
+      <c r="Q13" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="R13" s="4">
         <f>1.14*5.678263243</f>
         <v>6.4732200970199996</v>
       </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <f>0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="V13" s="4">
+      <c r="W13" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W13" s="20">
+      <c r="X13" s="20">
         <f>2349*0.062427961</f>
         <v>146.64328038899998</v>
       </c>
-      <c r="X13" s="4">
+      <c r="Y13" s="4">
         <f>1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>1037</v>
       </c>
-      <c r="AB13" s="4">
+      <c r="AC13" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC13" s="18">
+      <c r="AD13" s="18">
         <f>800* 0.000239005736</f>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AD13" s="4">
-        <f t="shared" ref="AD13:AD21" si="14">840* 0.000239005736</f>
+      <c r="AE13" s="4">
+        <f t="shared" ref="AE13:AE21" si="14">840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1041</v>
       </c>
@@ -10423,73 +10649,76 @@
         <v>1042</v>
       </c>
       <c r="C14" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D14" t="s">
         <v>1043</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>1000</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1005</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>1001</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K14" s="4">
+      <c r="L14" s="4">
         <f>CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P14" s="4">
+      <c r="Q14" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="R14" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <f t="shared" si="6"/>
         <v>5.5646979781399999</v>
       </c>
-      <c r="V14" s="4">
+      <c r="W14" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W14" s="20">
+      <c r="X14" s="20">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="X14" s="4">
+      <c r="Y14" s="4">
         <f>2349*0.062427961</f>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>1041</v>
       </c>
-      <c r="AB14" s="4">
+      <c r="AC14" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC14" s="18">
+      <c r="AD14" s="18">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD14" s="4">
+      <c r="AE14" s="4">
         <f>800* 0.000239005736</f>
         <v>0.19120458879999999</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1044</v>
       </c>
@@ -10497,73 +10726,76 @@
         <v>1045</v>
       </c>
       <c r="C15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D15" t="s">
         <v>1046</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>1000</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>1012</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>1001</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <f>CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P15" s="4">
+      <c r="Q15" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <f>1.41*5.678263243</f>
         <v>8.0063511726299996</v>
       </c>
-      <c r="V15" s="4">
+      <c r="W15" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W15" s="20">
+      <c r="X15" s="20">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X15" s="4">
+      <c r="Y15" s="4">
         <f>2349*0.062427961</f>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>1044</v>
       </c>
-      <c r="AB15" s="4">
+      <c r="AC15" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC15" s="18">
+      <c r="AD15" s="18">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD15" s="4">
-        <f t="shared" ref="AD15:AD20" si="15">300* 0.000239005736</f>
+      <c r="AE15" s="4">
+        <f t="shared" ref="AE15:AE20" si="15">300* 0.000239005736</f>
         <v>7.1701720799999993E-2</v>
       </c>
-      <c r="AH15">
+      <c r="AI15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1047</v>
       </c>
@@ -10571,73 +10803,76 @@
         <v>1048</v>
       </c>
       <c r="C16" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D16" t="s">
         <v>1049</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>1000</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1012</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>1001</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K16" s="4">
+      <c r="L16" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="L16" s="4">
-        <f t="shared" ref="L16:L20" si="16">CONVERT(200,"mm","ft")</f>
+      <c r="M16" s="4">
+        <f t="shared" ref="M16:M20" si="16">CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P16" s="4">
+      <c r="Q16" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="R16" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R16" s="4">
-        <f t="shared" ref="R16:R20" si="17">1.41*5.678263243</f>
+      <c r="S16" s="4">
+        <f t="shared" ref="S16:S20" si="17">1.41*5.678263243</f>
         <v>8.0063511726299996</v>
       </c>
-      <c r="V16" s="4">
+      <c r="W16" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W16" s="20">
+      <c r="X16" s="20">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X16" s="4">
+      <c r="Y16" s="4">
         <f>2349*0.062427961</f>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>1047</v>
       </c>
-      <c r="AB16" s="4">
+      <c r="AC16" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC16" s="18">
-        <f t="shared" ref="AC16:AC20" si="18">1213* 0.000239005736</f>
+      <c r="AD16" s="18">
+        <f t="shared" ref="AD16:AD20" si="18">1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AD16" s="4">
+      <c r="AE16" s="4">
         <f t="shared" si="15"/>
         <v>7.1701720799999993E-2</v>
       </c>
-      <c r="AH16">
+      <c r="AI16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1050</v>
       </c>
@@ -10645,73 +10880,76 @@
         <v>1051</v>
       </c>
       <c r="C17" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D17" t="s">
         <v>1052</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>1000</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1005</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>1001</v>
       </c>
-      <c r="J17" s="4">
+      <c r="K17" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K17" s="4">
+      <c r="L17" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="4">
         <f t="shared" si="16"/>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P17" s="4">
+      <c r="Q17" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <f t="shared" si="17"/>
         <v>8.0063511726299996</v>
       </c>
-      <c r="V17" s="4">
+      <c r="W17" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W17" s="20">
+      <c r="X17" s="20">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="X17" s="4">
-        <f t="shared" ref="X17:X20" si="19">2349*0.062427961</f>
+      <c r="Y17" s="4">
+        <f t="shared" ref="Y17:Y20" si="19">2349*0.062427961</f>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>1050</v>
       </c>
-      <c r="AB17" s="4">
+      <c r="AC17" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC17" s="18">
+      <c r="AD17" s="18">
         <f t="shared" si="18"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AD17" s="4">
+      <c r="AE17" s="4">
         <f t="shared" si="15"/>
         <v>7.1701720799999993E-2</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1053</v>
       </c>
@@ -10719,73 +10957,76 @@
         <v>1054</v>
       </c>
       <c r="C18" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D18" t="s">
         <v>1055</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>1000</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1005</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>1001</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K18" s="4">
+      <c r="L18" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="L18" s="4">
+      <c r="M18" s="4">
         <f t="shared" si="16"/>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P18" s="4">
+      <c r="Q18" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q18" s="4">
-        <f t="shared" ref="Q18" si="20">0.03*5.678263243</f>
+      <c r="R18" s="4">
+        <f t="shared" ref="R18" si="20">0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <f t="shared" si="17"/>
         <v>8.0063511726299996</v>
       </c>
-      <c r="V18" s="4">
+      <c r="W18" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W18" s="20">
+      <c r="X18" s="20">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="X18" s="4">
+      <c r="Y18" s="4">
         <f t="shared" si="19"/>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>1053</v>
       </c>
-      <c r="AB18" s="4">
+      <c r="AC18" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC18" s="18">
+      <c r="AD18" s="18">
         <f t="shared" si="18"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AD18" s="4">
+      <c r="AE18" s="4">
         <f t="shared" si="15"/>
         <v>7.1701720799999993E-2</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1056</v>
       </c>
@@ -10793,73 +11034,76 @@
         <v>1057</v>
       </c>
       <c r="C19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D19" t="s">
         <v>1058</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>1000</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1012</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>1001</v>
       </c>
-      <c r="J19" s="4">
+      <c r="K19" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K19" s="4">
+      <c r="L19" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="L19" s="4">
+      <c r="M19" s="4">
         <f t="shared" si="16"/>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P19" s="4">
+      <c r="Q19" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="R19" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <f t="shared" si="17"/>
         <v>8.0063511726299996</v>
       </c>
-      <c r="V19" s="4">
+      <c r="W19" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W19" s="20">
+      <c r="X19" s="20">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X19" s="4">
+      <c r="Y19" s="4">
         <f t="shared" si="19"/>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>1056</v>
       </c>
-      <c r="AB19" s="4">
+      <c r="AC19" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC19" s="18">
+      <c r="AD19" s="18">
         <f t="shared" si="18"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AD19" s="4">
+      <c r="AE19" s="4">
         <f t="shared" si="15"/>
         <v>7.1701720799999993E-2</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1059</v>
       </c>
@@ -10867,73 +11111,76 @@
         <v>1060</v>
       </c>
       <c r="C20" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D20" t="s">
         <v>1061</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>1000</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1012</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>1001</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K20" s="4">
+      <c r="L20" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="L20" s="4">
+      <c r="M20" s="4">
         <f t="shared" si="16"/>
         <v>0.65616797900262469</v>
       </c>
-      <c r="P20" s="4">
+      <c r="Q20" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <f t="shared" si="17"/>
         <v>8.0063511726299996</v>
       </c>
-      <c r="V20" s="4">
+      <c r="W20" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W20" s="20">
+      <c r="X20" s="20">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="X20" s="4">
+      <c r="Y20" s="4">
         <f t="shared" si="19"/>
         <v>146.64328038899998</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>1059</v>
       </c>
-      <c r="AB20" s="4">
+      <c r="AC20" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC20" s="18">
+      <c r="AD20" s="18">
         <f t="shared" si="18"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AD20" s="4">
+      <c r="AE20" s="4">
         <f t="shared" si="15"/>
         <v>7.1701720799999993E-2</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1062</v>
       </c>
@@ -10941,74 +11188,77 @@
         <v>1063</v>
       </c>
       <c r="C21" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D21" t="s">
         <v>1064</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>1000</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1065</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>1000</v>
       </c>
-      <c r="J21" s="4">
+      <c r="K21" s="4">
         <f t="shared" si="3"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K21" s="4">
+      <c r="L21" s="4">
         <f>CONVERT(200,"mm","ft")</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="L21" s="4">
+      <c r="M21" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P21" s="4">
+      <c r="Q21" s="4">
         <f t="shared" si="0"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="4">
         <f>1.58*5.678263243</f>
         <v>8.9716559239400002</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <f>0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="V21" s="4">
+      <c r="W21" s="4">
         <f t="shared" si="1"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W21" s="20">
+      <c r="X21" s="20">
         <f>2288*0.062427961</f>
         <v>142.835174768</v>
       </c>
-      <c r="X21" s="4">
+      <c r="Y21" s="4">
         <f>1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>1062</v>
       </c>
-      <c r="AB21" s="4">
+      <c r="AC21" s="4">
         <f t="shared" si="2"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC21" s="18">
+      <c r="AD21" s="18">
         <f>880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD21" s="4">
+      <c r="AE21" s="4">
         <f t="shared" si="14"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="K23" s="4"/>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="L23" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11017,23 +11267,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889CC4FE-153F-450B-8B96-60EE246EB7D1}">
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="33" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="34" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>963</v>
       </c>
@@ -11041,103 +11292,106 @@
         <v>964</v>
       </c>
       <c r="C1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D1" t="s">
         <v>965</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>966</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>967</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>968</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>969</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>970</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>971</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>972</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>973</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>974</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>975</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>976</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>977</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>978</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>979</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>980</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>981</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>982</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>983</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>984</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>985</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>986</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>987</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>988</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>989</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>990</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>991</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>992</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>993</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>994</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>995</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1086</v>
       </c>
@@ -11145,73 +11399,76 @@
         <v>1063</v>
       </c>
       <c r="C2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D2" t="s">
         <v>1064</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1000</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>1107</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>1065</v>
       </c>
-      <c r="J2" s="17">
+      <c r="K2" s="17">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K2" s="17">
+      <c r="L2" s="17">
         <f>CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L2" s="17">
+      <c r="M2" s="17">
         <f>CONVERT(150,"mm","ft")</f>
         <v>0.49212598425196852</v>
       </c>
-      <c r="P2" s="4">
+      <c r="Q2" s="4">
         <f>0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="R2" s="4">
         <f>0.8*5.678263243</f>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R2" s="4">
+      <c r="S2" s="4">
         <f>1.58*5.678263243</f>
         <v>8.9716559239400002</v>
       </c>
-      <c r="V2" s="4">
+      <c r="W2" s="4">
         <f>1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="W2" s="4">
+      <c r="X2" s="4">
         <f>1892*0.062427961</f>
         <v>118.11370221199999</v>
       </c>
-      <c r="X2" s="4">
+      <c r="Y2" s="4">
         <f>2288*0.062427961</f>
         <v>142.835174768</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AB2" s="21" t="s">
         <v>1086</v>
       </c>
-      <c r="AB2" s="4">
+      <c r="AC2" s="4">
         <f>840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AC2" s="18">
+      <c r="AD2" s="18">
         <f>880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD2" s="4">
+      <c r="AE2" s="4">
         <f>880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>1087</v>
       </c>
@@ -11219,73 +11476,76 @@
         <v>1066</v>
       </c>
       <c r="C3" t="s">
-        <v>1064</v>
+        <v>1133</v>
       </c>
       <c r="D3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E3" t="s">
         <v>1000</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1107</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>1108</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K3" s="17">
-        <f t="shared" ref="K3:K22" si="0">CONVERT(80,"mm","ft")</f>
+      <c r="L3" s="17">
+        <f t="shared" ref="L3:L22" si="0">CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="P3" s="4">
-        <f t="shared" ref="P3:P22" si="1">0.72*5.678263243</f>
+      <c r="Q3" s="4">
+        <f t="shared" ref="Q3:Q22" si="1">0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q3" s="4">
-        <f t="shared" ref="Q3:Q22" si="2">0.8*5.678263243</f>
+      <c r="R3" s="4">
+        <f t="shared" ref="R3:R22" si="2">0.8*5.678263243</f>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V3" s="4">
-        <f t="shared" ref="V3:V22" si="3">1762*0.062427961</f>
+      <c r="W3" s="4">
+        <f t="shared" ref="W3:W22" si="3">1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
-      <c r="W3" s="4">
-        <f t="shared" ref="W3:W22" si="4">1892*0.062427961</f>
+      <c r="X3" s="4">
+        <f t="shared" ref="X3:X22" si="4">1892*0.062427961</f>
         <v>118.11370221199999</v>
       </c>
-      <c r="X3" s="4">
+      <c r="Y3" s="4">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="AA3" s="22" t="s">
+      <c r="AB3" s="22" t="s">
         <v>1087</v>
       </c>
-      <c r="AB3" s="4">
-        <f t="shared" ref="AB3:AB22" si="5">840* 0.000239005736</f>
+      <c r="AC3" s="4">
+        <f t="shared" ref="AC3:AC22" si="5">840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="AC3" s="18">
-        <f t="shared" ref="AC3:AC22" si="6">880* 0.000239005736</f>
+      <c r="AD3" s="18">
+        <f t="shared" ref="AD3:AD22" si="6">880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD3" s="4">
+      <c r="AE3" s="4">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>1088</v>
       </c>
@@ -11293,73 +11553,76 @@
         <v>1067</v>
       </c>
       <c r="C4" t="s">
-        <v>1064</v>
+        <v>1134</v>
       </c>
       <c r="D4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E4" t="s">
         <v>1000</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>1107</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>1108</v>
       </c>
-      <c r="J4" s="4">
-        <f t="shared" ref="J4:J22" si="7">CONVERT(20,"mm","ft")</f>
+      <c r="K4" s="4">
+        <f t="shared" ref="K4:K22" si="7">CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K4" s="17">
+      <c r="L4" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="P4" s="4">
+      <c r="Q4" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="R4" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R4" s="4">
-        <f t="shared" ref="R4:R10" si="8">0.03*5.678263243</f>
+      <c r="S4" s="4">
+        <f t="shared" ref="S4:S10" si="8">0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V4" s="4">
+      <c r="W4" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W4" s="4">
+      <c r="X4" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X4" s="4">
-        <f t="shared" ref="X4:X6" si="9">35*0.062427961</f>
+      <c r="Y4" s="4">
+        <f t="shared" ref="Y4:Y6" si="9">35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
-      <c r="AA4" s="22" t="s">
+      <c r="AB4" s="22" t="s">
         <v>1088</v>
       </c>
-      <c r="AB4" s="4">
+      <c r="AC4" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC4" s="18">
+      <c r="AD4" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD4" s="4">
-        <f t="shared" ref="AD4:AD6" si="10">1213* 0.000239005736</f>
+      <c r="AE4" s="4">
+        <f t="shared" ref="AE4:AE6" si="10">1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>1089</v>
       </c>
@@ -11367,73 +11630,76 @@
         <v>1068</v>
       </c>
       <c r="C5" t="s">
-        <v>1064</v>
+        <v>1153</v>
       </c>
       <c r="D5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E5" t="s">
         <v>1000</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>1107</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>1108</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K5" s="17">
+      <c r="L5" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <f>CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="R5" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V5" s="4">
+      <c r="W5" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W5" s="4">
+      <c r="X5" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X5" s="4">
+      <c r="Y5" s="4">
         <f t="shared" si="9"/>
         <v>2.1849786349999998</v>
       </c>
-      <c r="AA5" s="22" t="s">
+      <c r="AB5" s="22" t="s">
         <v>1089</v>
       </c>
-      <c r="AB5" s="4">
+      <c r="AC5" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC5" s="18">
+      <c r="AD5" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD5" s="4">
+      <c r="AE5" s="4">
         <f t="shared" si="10"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>1090</v>
       </c>
@@ -11441,73 +11707,76 @@
         <v>1069</v>
       </c>
       <c r="C6" t="s">
-        <v>1064</v>
+        <v>1154</v>
       </c>
       <c r="D6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E6" t="s">
         <v>1000</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>1107</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>1108</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K6" s="17">
+      <c r="L6" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <f>CONVERT(100,"mm","ft")</f>
         <v>0.32808398950131235</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="R6" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V6" s="4">
+      <c r="W6" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W6" s="4">
+      <c r="X6" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X6" s="4">
+      <c r="Y6" s="4">
         <f t="shared" si="9"/>
         <v>2.1849786349999998</v>
       </c>
-      <c r="AA6" s="22" t="s">
+      <c r="AB6" s="22" t="s">
         <v>1090</v>
       </c>
-      <c r="AB6" s="4">
+      <c r="AC6" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC6" s="18">
+      <c r="AD6" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD6" s="4">
+      <c r="AE6" s="4">
         <f t="shared" si="10"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>1091</v>
       </c>
@@ -11515,73 +11784,76 @@
         <v>1070</v>
       </c>
       <c r="C7" t="s">
-        <v>1064</v>
+        <v>1155</v>
       </c>
       <c r="D7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E7" t="s">
         <v>1000</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1107</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>1029</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K7" s="17">
+      <c r="L7" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="P7" s="4">
+      <c r="Q7" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="R7" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V7" s="4">
+      <c r="W7" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W7" s="4">
+      <c r="X7" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X7" s="4">
+      <c r="Y7" s="4">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
-      <c r="AA7" s="22" t="s">
+      <c r="AB7" s="22" t="s">
         <v>1091</v>
       </c>
-      <c r="AB7" s="4">
+      <c r="AC7" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC7" s="18">
+      <c r="AD7" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD7" s="4">
+      <c r="AE7" s="4">
         <f>1590* 0.000239005736</f>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>1092</v>
       </c>
@@ -11589,73 +11861,76 @@
         <v>1071</v>
       </c>
       <c r="C8" t="s">
-        <v>1064</v>
+        <v>1156</v>
       </c>
       <c r="D8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E8" t="s">
         <v>1000</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>1107</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>1029</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K8" s="17">
+      <c r="L8" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="P8" s="4">
+      <c r="Q8" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V8" s="4">
+      <c r="W8" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W8" s="4">
+      <c r="X8" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X8" s="4">
-        <f t="shared" ref="X8:X10" si="11">40*0.062427961</f>
+      <c r="Y8" s="4">
+        <f t="shared" ref="Y8:Y10" si="11">40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
-      <c r="AA8" s="22" t="s">
+      <c r="AB8" s="22" t="s">
         <v>1092</v>
       </c>
-      <c r="AB8" s="4">
+      <c r="AC8" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC8" s="18">
+      <c r="AD8" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD8" s="4">
-        <f t="shared" ref="AD8:AD10" si="12">1590* 0.000239005736</f>
+      <c r="AE8" s="4">
+        <f t="shared" ref="AE8:AE10" si="12">1590* 0.000239005736</f>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>1093</v>
       </c>
@@ -11663,73 +11938,76 @@
         <v>1072</v>
       </c>
       <c r="C9" t="s">
-        <v>1064</v>
+        <v>1157</v>
       </c>
       <c r="D9" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E9" t="s">
         <v>1000</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>1107</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>1029</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K9" s="17">
+      <c r="L9" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <f>CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
-      <c r="P9" s="4">
+      <c r="Q9" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="R9" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V9" s="4">
+      <c r="W9" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W9" s="4">
+      <c r="X9" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X9" s="4">
+      <c r="Y9" s="4">
         <f t="shared" si="11"/>
         <v>2.4971184399999999</v>
       </c>
-      <c r="AA9" s="22" t="s">
+      <c r="AB9" s="22" t="s">
         <v>1093</v>
       </c>
-      <c r="AB9" s="4">
+      <c r="AC9" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC9" s="18">
+      <c r="AD9" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD9" s="4">
+      <c r="AE9" s="4">
         <f t="shared" si="12"/>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>1094</v>
       </c>
@@ -11737,73 +12015,76 @@
         <v>1073</v>
       </c>
       <c r="C10" t="s">
-        <v>1064</v>
+        <v>1158</v>
       </c>
       <c r="D10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E10" t="s">
         <v>1000</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>1107</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>1029</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K10" s="17">
+      <c r="L10" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <f>CONVERT(100,"mm","ft")</f>
         <v>0.32808398950131235</v>
       </c>
-      <c r="P10" s="4">
+      <c r="Q10" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="R10" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="V10" s="4">
+      <c r="W10" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W10" s="4">
+      <c r="X10" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X10" s="4">
+      <c r="Y10" s="4">
         <f t="shared" si="11"/>
         <v>2.4971184399999999</v>
       </c>
-      <c r="AA10" s="22" t="s">
+      <c r="AB10" s="22" t="s">
         <v>1094</v>
       </c>
-      <c r="AB10" s="4">
+      <c r="AC10" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC10" s="18">
+      <c r="AD10" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD10" s="4">
+      <c r="AE10" s="4">
         <f t="shared" si="12"/>
         <v>0.38001912024000001</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>1095</v>
       </c>
@@ -11811,73 +12092,76 @@
         <v>1074</v>
       </c>
       <c r="C11" t="s">
-        <v>1064</v>
+        <v>1159</v>
       </c>
       <c r="D11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E11" t="s">
         <v>1000</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>1107</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>1108</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K11" s="17">
+      <c r="L11" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
         <f>CONVERT(0,"mm","ft")</f>
         <v>0</v>
       </c>
-      <c r="P11" s="4">
+      <c r="Q11" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="R11" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="V11" s="4">
+      <c r="W11" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W11" s="4">
+      <c r="X11" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X11" s="4">
+      <c r="Y11" s="4">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="AA11" s="22" t="s">
+      <c r="AB11" s="22" t="s">
         <v>1095</v>
       </c>
-      <c r="AB11" s="4">
+      <c r="AC11" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC11" s="18">
+      <c r="AD11" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD11" s="4">
+      <c r="AE11" s="4">
         <f>1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>1096</v>
       </c>
@@ -11885,73 +12169,76 @@
         <v>1075</v>
       </c>
       <c r="C12" t="s">
-        <v>1064</v>
+        <v>1160</v>
       </c>
       <c r="D12" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E12" t="s">
         <v>1000</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>1107</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>1108</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K12" s="17">
+      <c r="L12" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
         <f>CONVERT(10,"mm","ft")</f>
         <v>3.2808398950131233E-2</v>
       </c>
-      <c r="P12" s="4">
+      <c r="Q12" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="R12" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R12" s="4">
-        <f t="shared" ref="R12:R22" si="13">0.04*5.678263243</f>
+      <c r="S12" s="4">
+        <f t="shared" ref="S12:S22" si="13">0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="V12" s="4">
+      <c r="W12" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W12" s="4">
+      <c r="X12" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X12" s="4">
-        <f t="shared" ref="X12:X22" si="14">28*0.062427961</f>
+      <c r="Y12" s="4">
+        <f t="shared" ref="Y12:Y22" si="14">28*0.062427961</f>
         <v>1.747982908</v>
       </c>
-      <c r="AA12" s="22" t="s">
+      <c r="AB12" s="22" t="s">
         <v>1096</v>
       </c>
-      <c r="AB12" s="4">
+      <c r="AC12" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC12" s="18">
+      <c r="AD12" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD12" s="4">
-        <f t="shared" ref="AD12:AD22" si="15">1213* 0.000239005736</f>
+      <c r="AE12" s="4">
+        <f t="shared" ref="AE12:AE22" si="15">1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>1097</v>
       </c>
@@ -11959,73 +12246,76 @@
         <v>1076</v>
       </c>
       <c r="C13" t="s">
-        <v>1064</v>
+        <v>1161</v>
       </c>
       <c r="D13" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E13" t="s">
         <v>1000</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1107</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>1108</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K13" s="17">
+      <c r="L13" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L13" s="4">
-        <f t="shared" ref="L13:L15" si="16">CONVERT(10,"mm","ft")</f>
+      <c r="M13" s="4">
+        <f t="shared" ref="M13:M15" si="16">CONVERT(10,"mm","ft")</f>
         <v>3.2808398950131233E-2</v>
       </c>
-      <c r="P13" s="4">
+      <c r="Q13" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="R13" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V13" s="4">
+      <c r="W13" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W13" s="4">
+      <c r="X13" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X13" s="4">
+      <c r="Y13" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA13" s="22" t="s">
+      <c r="AB13" s="22" t="s">
         <v>1097</v>
       </c>
-      <c r="AB13" s="4">
+      <c r="AC13" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC13" s="18">
+      <c r="AD13" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD13" s="4">
+      <c r="AE13" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>1098</v>
       </c>
@@ -12033,73 +12323,76 @@
         <v>1077</v>
       </c>
       <c r="C14" t="s">
-        <v>1064</v>
+        <v>1162</v>
       </c>
       <c r="D14" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E14" t="s">
         <v>1000</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1107</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>1108</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K14" s="17">
+      <c r="L14" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="4">
         <f t="shared" si="16"/>
         <v>3.2808398950131233E-2</v>
       </c>
-      <c r="P14" s="4">
+      <c r="Q14" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="R14" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V14" s="4">
+      <c r="W14" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W14" s="4">
+      <c r="X14" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X14" s="4">
+      <c r="Y14" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA14" s="22" t="s">
+      <c r="AB14" s="22" t="s">
         <v>1098</v>
       </c>
-      <c r="AB14" s="4">
+      <c r="AC14" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC14" s="18">
+      <c r="AD14" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD14" s="4">
+      <c r="AE14" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>1099</v>
       </c>
@@ -12107,73 +12400,76 @@
         <v>1078</v>
       </c>
       <c r="C15" t="s">
-        <v>1064</v>
+        <v>1163</v>
       </c>
       <c r="D15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E15" t="s">
         <v>1000</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>1107</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>1108</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K15" s="17">
+      <c r="L15" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <f t="shared" si="16"/>
         <v>3.2808398950131233E-2</v>
       </c>
-      <c r="P15" s="4">
+      <c r="Q15" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V15" s="4">
+      <c r="W15" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W15" s="4">
+      <c r="X15" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X15" s="4">
+      <c r="Y15" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA15" s="22" t="s">
+      <c r="AB15" s="22" t="s">
         <v>1099</v>
       </c>
-      <c r="AB15" s="4">
+      <c r="AC15" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC15" s="18">
+      <c r="AD15" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD15" s="4">
+      <c r="AE15" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH15">
+      <c r="AI15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>1100</v>
       </c>
@@ -12181,73 +12477,76 @@
         <v>1079</v>
       </c>
       <c r="C16" t="s">
-        <v>1064</v>
+        <v>1164</v>
       </c>
       <c r="D16" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E16" t="s">
         <v>1000</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1107</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>1108</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K16" s="17">
+      <c r="L16" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L16" s="4">
-        <f t="shared" ref="L16:L18" si="17">CONVERT(20,"mm","ft")</f>
+      <c r="M16" s="4">
+        <f t="shared" ref="M16:M18" si="17">CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P16" s="4">
+      <c r="Q16" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="R16" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V16" s="4">
+      <c r="W16" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W16" s="4">
+      <c r="X16" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X16" s="4">
+      <c r="Y16" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA16" s="22" t="s">
+      <c r="AB16" s="22" t="s">
         <v>1100</v>
       </c>
-      <c r="AB16" s="4">
+      <c r="AC16" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC16" s="18">
+      <c r="AD16" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD16" s="4">
+      <c r="AE16" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH16">
+      <c r="AI16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>1101</v>
       </c>
@@ -12255,73 +12554,76 @@
         <v>1080</v>
       </c>
       <c r="C17" t="s">
-        <v>1064</v>
+        <v>1165</v>
       </c>
       <c r="D17" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E17" t="s">
         <v>1000</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1107</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>1108</v>
       </c>
-      <c r="J17" s="4">
+      <c r="K17" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K17" s="17">
+      <c r="L17" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="4">
         <f t="shared" si="17"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P17" s="4">
+      <c r="Q17" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V17" s="4">
+      <c r="W17" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W17" s="4">
+      <c r="X17" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X17" s="4">
+      <c r="Y17" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA17" s="22" t="s">
+      <c r="AB17" s="22" t="s">
         <v>1101</v>
       </c>
-      <c r="AB17" s="4">
+      <c r="AC17" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC17" s="18">
+      <c r="AD17" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD17" s="4">
+      <c r="AE17" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>1102</v>
       </c>
@@ -12329,73 +12631,76 @@
         <v>1081</v>
       </c>
       <c r="C18" t="s">
-        <v>1064</v>
+        <v>1166</v>
       </c>
       <c r="D18" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E18" t="s">
         <v>1000</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1107</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>1108</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K18" s="17">
+      <c r="L18" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L18" s="4">
+      <c r="M18" s="4">
         <f t="shared" si="17"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="P18" s="4">
+      <c r="Q18" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="R18" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V18" s="4">
+      <c r="W18" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W18" s="4">
+      <c r="X18" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X18" s="4">
+      <c r="Y18" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA18" s="22" t="s">
+      <c r="AB18" s="22" t="s">
         <v>1102</v>
       </c>
-      <c r="AB18" s="4">
+      <c r="AC18" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC18" s="18">
+      <c r="AD18" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD18" s="4">
+      <c r="AE18" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
         <v>1103</v>
       </c>
@@ -12403,73 +12708,76 @@
         <v>1082</v>
       </c>
       <c r="C19" t="s">
-        <v>1064</v>
+        <v>1167</v>
       </c>
       <c r="D19" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E19" t="s">
         <v>1000</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1107</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>1108</v>
       </c>
-      <c r="J19" s="4">
+      <c r="K19" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K19" s="17">
+      <c r="L19" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L19" s="4">
+      <c r="M19" s="4">
         <f>CONVERT(30,"mm","ft")</f>
         <v>9.8425196850393706E-2</v>
       </c>
-      <c r="P19" s="4">
+      <c r="Q19" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="R19" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V19" s="4">
+      <c r="W19" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W19" s="4">
+      <c r="X19" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X19" s="4">
+      <c r="Y19" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA19" s="22" t="s">
+      <c r="AB19" s="22" t="s">
         <v>1103</v>
       </c>
-      <c r="AB19" s="4">
+      <c r="AC19" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC19" s="18">
+      <c r="AD19" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD19" s="4">
+      <c r="AE19" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>1104</v>
       </c>
@@ -12477,73 +12785,76 @@
         <v>1083</v>
       </c>
       <c r="C20" t="s">
-        <v>1064</v>
+        <v>1168</v>
       </c>
       <c r="D20" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E20" t="s">
         <v>1000</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1107</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>1108</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K20" s="17">
+      <c r="L20" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L20" s="4">
+      <c r="M20" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="P20" s="4">
+      <c r="Q20" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V20" s="4">
+      <c r="W20" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W20" s="4">
+      <c r="X20" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X20" s="4">
+      <c r="Y20" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA20" s="22" t="s">
+      <c r="AB20" s="22" t="s">
         <v>1104</v>
       </c>
-      <c r="AB20" s="4">
+      <c r="AC20" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC20" s="18">
+      <c r="AD20" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD20" s="4">
+      <c r="AE20" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>1105</v>
       </c>
@@ -12551,73 +12862,76 @@
         <v>1084</v>
       </c>
       <c r="C21" t="s">
-        <v>1064</v>
+        <v>1169</v>
       </c>
       <c r="D21" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E21" t="s">
         <v>1000</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1107</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>1108</v>
       </c>
-      <c r="J21" s="4">
+      <c r="K21" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K21" s="17">
+      <c r="L21" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L21" s="4">
+      <c r="M21" s="4">
         <f>CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
-      <c r="P21" s="4">
+      <c r="Q21" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V21" s="4">
+      <c r="W21" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W21" s="4">
+      <c r="X21" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X21" s="4">
+      <c r="Y21" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA21" s="22" t="s">
+      <c r="AB21" s="22" t="s">
         <v>1105</v>
       </c>
-      <c r="AB21" s="4">
+      <c r="AC21" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC21" s="18">
+      <c r="AD21" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD21" s="4">
+      <c r="AE21" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>1106</v>
       </c>
@@ -12625,74 +12939,77 @@
         <v>1085</v>
       </c>
       <c r="C22" t="s">
-        <v>1064</v>
+        <v>1170</v>
       </c>
       <c r="D22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E22" t="s">
         <v>1000</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1107</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>1108</v>
       </c>
-      <c r="J22" s="4">
+      <c r="K22" s="4">
         <f t="shared" si="7"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="K22" s="17">
+      <c r="L22" s="17">
         <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="L22" s="4">
+      <c r="M22" s="4">
         <f>CONVERT(100,"mm","ft")</f>
         <v>0.32808398950131235</v>
       </c>
-      <c r="P22" s="4">
+      <c r="Q22" s="4">
         <f t="shared" si="1"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="R22" s="4">
         <f t="shared" si="2"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="R22" s="4">
+      <c r="S22" s="4">
         <f t="shared" si="13"/>
         <v>0.22713052972</v>
       </c>
-      <c r="V22" s="4">
+      <c r="W22" s="4">
         <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
-      <c r="W22" s="4">
+      <c r="X22" s="4">
         <f t="shared" si="4"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="X22" s="4">
+      <c r="Y22" s="4">
         <f t="shared" si="14"/>
         <v>1.747982908</v>
       </c>
-      <c r="AA22" s="22" t="s">
+      <c r="AB22" s="22" t="s">
         <v>1106</v>
       </c>
-      <c r="AB22" s="4">
+      <c r="AC22" s="4">
         <f t="shared" si="5"/>
         <v>0.20076481824</v>
       </c>
-      <c r="AC22" s="18">
+      <c r="AD22" s="18">
         <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AD22" s="4">
+      <c r="AE22" s="4">
         <f t="shared" si="15"/>
         <v>0.289913957768</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="K23" s="4"/>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="L23" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/database/ML_ScaleUp_v02.xlsx
+++ b/database/ML_ScaleUp_v02.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\S2501 ECM Generator\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\S2302 eQuest Automation\S2302.4 ECM Generator\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B5171E-9FD3-4774-A19F-059900D8556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111F518F-1159-47EF-8FF7-9B6DCE1C209A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialDb-ENS2018" sheetId="1" r:id="rId1"/>
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="1172">
   <si>
     <t>City</t>
   </si>
@@ -3965,6 +3965,9 @@
   </si>
   <si>
     <t>RC200_EPS100</t>
+  </si>
+  <si>
+    <t>Glass-Types</t>
   </si>
 </sst>
 </file>
@@ -4152,12 +4155,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4314,24 +4320,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D0B1C4E7-375E-428E-A5E9-E1083194D512}" name="CostDB" displayName="CostDB" ref="A1:F20" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D0B1C4E7-375E-428E-A5E9-E1083194D512}" name="CostDB" displayName="CostDB" ref="A1:F20" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:F20" xr:uid="{D0B1C4E7-375E-428E-A5E9-E1083194D512}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7AB808BB-ED43-466A-80D6-AEFF15EA521A}" name="Material" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{5000B84A-F0AE-4B85-AB3D-E13EB1E11392}" name="Cost" dataDxfId="11" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{2B8EB297-2021-4612-9273-022A7F0BEA94}" name="Unit" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{A0D3802B-2C8C-4A18-8970-D383A670E786}" name="Cost (per m2 for unit thickness)" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{7AB808BB-ED43-466A-80D6-AEFF15EA521A}" name="Material" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{5000B84A-F0AE-4B85-AB3D-E13EB1E11392}" name="Cost" dataDxfId="12" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{2B8EB297-2021-4612-9273-022A7F0BEA94}" name="Unit" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{A0D3802B-2C8C-4A18-8970-D383A670E786}" name="Cost (per m2 for unit thickness)" dataDxfId="10">
       <calculatedColumnFormula>B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{781C6105-6CBC-4496-97F2-F3B85651C231}" name="Fixed Cost/m2" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{1D676315-1930-4AA8-982E-7434F4268443}" name="Source" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{781C6105-6CBC-4496-97F2-F3B85651C231}" name="Fixed Cost/m2" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{1D676315-1930-4AA8-982E-7434F4268443}" name="Source" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9919ACC9-777A-40E3-B26D-DDAE1858D3CC}" name="WorkingDB" displayName="WorkingDB" ref="A1:L70" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9919ACC9-777A-40E3-B26D-DDAE1858D3CC}" name="WorkingDB" displayName="WorkingDB" ref="A1:L70" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:L70" xr:uid="{9919ACC9-777A-40E3-B26D-DDAE1858D3CC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L40">
     <sortCondition ref="A1:A40"/>
@@ -4346,7 +4352,7 @@
     <tableColumn id="7" xr3:uid="{18F2EF1C-D54D-40A5-B82E-FC925BF0144C}" name="Cost _x000a_(Rs/m2 of Surface Area for 1m thickness)">
       <calculatedColumnFormula>VLOOKUP(WorkingDB[[#This Row],[Material]],CostDB[#Data],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{975AF750-E3AC-4BB7-B7CC-9ABD6A7C482A}" name="Thermal Diffusivity_x000a_(m2/s)" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{975AF750-E3AC-4BB7-B7CC-9ABD6A7C482A}" name="Thermal Diffusivity_x000a_(m2/s)" dataDxfId="6">
       <calculatedColumnFormula>B2/(D2*C2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{985080FA-E5BA-44B7-B505-26E1B2AA07A4}" name="Effusivity"/>
@@ -4359,25 +4365,28 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4EF59487-4868-4B73-A0EA-3FBBB5F3EDAB}" name="Table76" displayName="Table76" ref="A1:I35" totalsRowShown="0">
-  <autoFilter ref="A1:I35" xr:uid="{4EF59487-4868-4B73-A0EA-3FBBB5F3EDAB}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4EF59487-4868-4B73-A0EA-3FBBB5F3EDAB}" name="Table76" displayName="Table76" ref="A1:J35" totalsRowShown="0">
+  <autoFilter ref="A1:J35" xr:uid="{4EF59487-4868-4B73-A0EA-3FBBB5F3EDAB}"/>
+  <tableColumns count="10">
     <tableColumn id="2" xr3:uid="{01CFB6FC-0F8C-4A63-94FE-0EC5D1467A3F}" name="Glass Type"/>
     <tableColumn id="3" xr3:uid="{DA479A64-18F2-407E-BFE2-4B94CF85747C}" name="U-value (COG)"/>
     <tableColumn id="4" xr3:uid="{BB74D783-B5DC-4AE2-85D5-60A7231996E1}" name="GLASS-CONDUCT"/>
     <tableColumn id="6" xr3:uid="{8759EF74-95D6-4753-99BF-A7DB4DD1B597}" name="VIS-TRANS"/>
     <tableColumn id="5" xr3:uid="{0CF51170-62CE-419D-8E4C-82459E58DAB2}" name="Climate"/>
-    <tableColumn id="8" xr3:uid="{B0A1CC73-DDC9-4F92-876A-67DF0B25D0CE}" name="U-Value(IP)" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{B0A1CC73-DDC9-4F92-876A-67DF0B25D0CE}" name="U-Value(IP)" dataDxfId="5">
       <calculatedColumnFormula>Table76[[#This Row],[U-value (COG)]]/5.67</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6FDD2159-EE42-4E1B-BC9D-A8175C99276F}" name="SHADING-COEF" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{6FDD2159-EE42-4E1B-BC9D-A8175C99276F}" name="SHADING-COEF" dataDxfId="4">
       <calculatedColumnFormula>Table76[[#This Row],[GLASS-CONDUCT]]/0.87</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{A4747B72-B32D-46E0-AE1A-BF46A179B2F9}" name="Glass">
       <calculatedColumnFormula>IF(Table76[[#This Row],[Glass Type]]="Double Glazed","DG","SG")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0790EAAE-3AEB-4334-B47E-D050FCCFCFEA}" name="GLASS-TYPE" dataDxfId="2">
-      <calculatedColumnFormula>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
+    <tableColumn id="11" xr3:uid="{0790EAAE-3AEB-4334-B47E-D050FCCFCFEA}" name="GLASS-TYPE" dataDxfId="3">
+      <calculatedColumnFormula>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="1" xr3:uid="{CE52CB8C-40EC-4571-B677-7C72ACBBB22B}" name="Glass-Types" dataDxfId="2">
+      <calculatedColumnFormula>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -13019,7 +13028,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA75B1A1-D4AC-429A-BBEB-8A60D42B628B}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -13031,9 +13040,10 @@
     <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5546875" customWidth="1"/>
     <col min="9" max="9" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>220</v>
       </c>
@@ -13061,8 +13071,11 @@
       <c r="I1" t="s">
         <v>962</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -13091,11 +13104,15 @@
         <v>DG</v>
       </c>
       <c r="I2" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.18_0.57_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+      </c>
+      <c r="J2" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.5_0.57_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -13124,11 +13141,15 @@
         <v>DG</v>
       </c>
       <c r="I3" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.18_0.69_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+      </c>
+      <c r="J3" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.6_0.69_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -13157,11 +13178,15 @@
         <v>DG</v>
       </c>
       <c r="I4" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.18_0.8_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+      </c>
+      <c r="J4" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.7_0.8_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -13190,11 +13215,15 @@
         <v>DG</v>
       </c>
       <c r="I5" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.26_0.57_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+      </c>
+      <c r="J5" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.5_0.57_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -13223,11 +13252,15 @@
         <v>DG</v>
       </c>
       <c r="I6" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.26_0.69_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+      </c>
+      <c r="J6" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.6_0.69_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -13256,11 +13289,15 @@
         <v>DG</v>
       </c>
       <c r="I7" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.26_0.8_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+      </c>
+      <c r="J7" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.7_0.8_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -13289,11 +13326,15 @@
         <v>DG</v>
       </c>
       <c r="I8" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.44_0.57_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+      </c>
+      <c r="J8" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.5_0.57_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -13322,11 +13363,15 @@
         <v>DG</v>
       </c>
       <c r="I9" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.44_0.69_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+      </c>
+      <c r="J9" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.6_0.69_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -13355,11 +13400,15 @@
         <v>DG</v>
       </c>
       <c r="I10" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.44_0.8_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+      </c>
+      <c r="J10" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.7_0.8_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -13388,11 +13437,15 @@
         <v>DG</v>
       </c>
       <c r="I11" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.63_0.57_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+      </c>
+      <c r="J11" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.5_0.57_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -13421,11 +13474,15 @@
         <v>DG</v>
       </c>
       <c r="I12" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.63_0.69_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+      </c>
+      <c r="J12" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.6_0.69_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -13454,11 +13511,15 @@
         <v>DG</v>
       </c>
       <c r="I13" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.63_0.8_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+      </c>
+      <c r="J13" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.7_0.8_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -13487,11 +13548,15 @@
         <v>SG</v>
       </c>
       <c r="I14" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.57_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.5_0.57_0.4_Cold</v>
+      </c>
+      <c r="J14" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.5_0.57_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -13520,11 +13585,15 @@
         <v>SG</v>
       </c>
       <c r="I15" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.69_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.6_0.69_0.4_Cold</v>
+      </c>
+      <c r="J15" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.6_0.69_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -13553,11 +13622,15 @@
         <v>SG</v>
       </c>
       <c r="I16" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.8_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.7_0.8_0.4_Cold</v>
+      </c>
+      <c r="J16" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.7_0.8_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -13586,11 +13659,15 @@
         <v>SG</v>
       </c>
       <c r="I17" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.57_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.5_0.57_0.4_Cold</v>
+      </c>
+      <c r="J17" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.5_0.57_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -13619,11 +13696,15 @@
         <v>SG</v>
       </c>
       <c r="I18" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.69_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.6_0.69_0.4_Cold</v>
+      </c>
+      <c r="J18" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.6_0.69_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -13652,11 +13733,15 @@
         <v>SG</v>
       </c>
       <c r="I19" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.8_0.4_Cold</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.7_0.8_0.4_Cold</v>
+      </c>
+      <c r="J19" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.7_0.8_0.4_Cold</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -13685,11 +13770,15 @@
         <v>SG</v>
       </c>
       <c r="I20" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.67_0.34_0.4_Others</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.3_0.34_0.4_Others</v>
+      </c>
+      <c r="J20" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.3_0.34_0.4_Others</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -13718,11 +13807,15 @@
         <v>SG</v>
       </c>
       <c r="I21" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.34_0.4_Others</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.3_0.34_0.4_Others</v>
+      </c>
+      <c r="J21" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.3_0.34_0.4_Others</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -13751,11 +13844,15 @@
         <v>SG</v>
       </c>
       <c r="I22" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.46_0.4_Others</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.4_0.46_0.4_Others</v>
+      </c>
+      <c r="J22" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.4_0.46_0.4_Others</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -13784,11 +13881,15 @@
         <v>SG</v>
       </c>
       <c r="I23" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.57_0.4_Others</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.5_0.57_0.4_Others</v>
+      </c>
+      <c r="J23" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.5_0.57_0.4_Others</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -13817,11 +13918,15 @@
         <v>SG</v>
       </c>
       <c r="I24" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.69_0.4_Others</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.6_0.69_0.4_Others</v>
+      </c>
+      <c r="J24" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.6_0.69_0.4_Others</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -13850,11 +13955,15 @@
         <v>SG</v>
       </c>
       <c r="I25" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.85_0.8_0.4_Others</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.7_0.8_0.4_Others</v>
+      </c>
+      <c r="J25" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.7_0.8_0.4_Others</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -13883,11 +13992,15 @@
         <v>SG</v>
       </c>
       <c r="I26" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.34_0.4_Others</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.3_0.34_0.4_Others</v>
+      </c>
+      <c r="J26" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.3_0.34_0.4_Others</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -13916,11 +14029,15 @@
         <v>SG</v>
       </c>
       <c r="I27" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.46_0.4_Others</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.4_0.46_0.4_Others</v>
+      </c>
+      <c r="J27" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.4_0.46_0.4_Others</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -13949,11 +14066,15 @@
         <v>SG</v>
       </c>
       <c r="I28" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.57_0.4_Others</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.5_0.57_0.4_Others</v>
+      </c>
+      <c r="J28" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.5_0.57_0.4_Others</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -13982,11 +14103,15 @@
         <v>SG</v>
       </c>
       <c r="I29" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.69_0.4_Others</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.6_0.69_0.4_Others</v>
+      </c>
+      <c r="J29" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.6_0.69_0.4_Others</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>25</v>
       </c>
@@ -14015,11 +14140,15 @@
         <v>SG</v>
       </c>
       <c r="I30" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_1.01_0.8_0.4_Others</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.7_0.8_0.4_Others</v>
+      </c>
+      <c r="J30" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>SG_0.7_0.8_0.4_Others</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -14048,11 +14177,15 @@
         <v>DG</v>
       </c>
       <c r="I31" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.49_0.23_0.4_Others</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.2_0.23_0.4_Others</v>
+      </c>
+      <c r="J31" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.2_0.23_0.4_Others</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -14081,11 +14214,15 @@
         <v>DG</v>
       </c>
       <c r="I32" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.49_0.34_0.4_Others</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.3_0.34_0.4_Others</v>
+      </c>
+      <c r="J32" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.3_0.34_0.4_Others</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -14114,11 +14251,15 @@
         <v>DG</v>
       </c>
       <c r="I33" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.49_0.46_0.4_Others</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.4_0.46_0.4_Others</v>
+      </c>
+      <c r="J33" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.4_0.46_0.4_Others</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -14147,11 +14288,15 @@
         <v>DG</v>
       </c>
       <c r="I34" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.49_0.57_0.4_Others</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.5_0.57_0.4_Others</v>
+      </c>
+      <c r="J34" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.5_0.57_0.4_Others</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -14180,8 +14325,12 @@
         <v>DG</v>
       </c>
       <c r="I35" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.49_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.6_0.69_0.4_Others</v>
+      </c>
+      <c r="J35" t="str">
+        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>DG_0.6_0.69_0.4_Others</v>
       </c>
     </row>
   </sheetData>

--- a/database/ML_ScaleUp_v02.xlsx
+++ b/database/ML_ScaleUp_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\S2302 eQuest Automation\S2302.4 ECM Generator\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111F518F-1159-47EF-8FF7-9B6DCE1C209A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8063634C-4EA8-4158-8001-94FA0352D540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialDb-ENS2018" sheetId="1" r:id="rId1"/>
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="1113">
   <si>
     <t>City</t>
   </si>
@@ -3652,51 +3652,24 @@
     <t>ML_RCC</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_XPS25[ENS]</t>
-  </si>
-  <si>
-    <t>Reinforce_Concrete_200_XPS50[ENS]</t>
-  </si>
-  <si>
-    <t>Reinforce_Concrete_200_XPS75[ENS]</t>
-  </si>
-  <si>
-    <t>Reinforce_Concrete_200_XPS100[ENS]</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_PUF25[ENS]</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_PUF50[ENS]</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_PUF75[ENS]</t>
   </si>
   <si>
     <t>Reinforce_Concrete_200_PUF100[ENS]</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_EPS2.5[ENS]</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_EPS5[ENS]</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_EPS7.5[ENS]</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_EPS10[ENS]</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_EPS12.5[ENS]</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_EPS15[ENS]</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_EPS17.5[ENS]</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_EPS20[ENS]</t>
   </si>
   <si>
@@ -3709,57 +3682,27 @@
     <t>Reinforce_Concrete_200_EPS75[ENS]</t>
   </si>
   <si>
-    <t>Reinforce_Concrete_200_EPS100[ENS]</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
     <t>R6</t>
   </si>
   <si>
-    <t>R7</t>
-  </si>
-  <si>
     <t>R8</t>
   </si>
   <si>
     <t>R9</t>
   </si>
   <si>
-    <t>R10</t>
-  </si>
-  <si>
     <t>R11</t>
   </si>
   <si>
-    <t>R12</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
-    <t>R14</t>
-  </si>
-  <si>
     <t>R15</t>
   </si>
   <si>
-    <t>R16</t>
-  </si>
-  <si>
     <t>R17</t>
   </si>
   <si>
@@ -3772,199 +3715,79 @@
     <t>R20</t>
   </si>
   <si>
-    <t>R21</t>
-  </si>
-  <si>
     <t>ML_B</t>
   </si>
   <si>
     <t>ML_EP</t>
   </si>
   <si>
+    <t>Roof-Name</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF75</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF100</t>
+  </si>
+  <si>
+    <t>ML_RC200_PUF25</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS5</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS10</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS15</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS20</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS25</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS50</t>
+  </si>
+  <si>
+    <t>ML_RC200_EPS75</t>
+  </si>
+  <si>
+    <t>RC200</t>
+  </si>
+  <si>
+    <t>RC200_PUF25</t>
+  </si>
+  <si>
+    <t>RC200_PUF75</t>
+  </si>
+  <si>
+    <t>RC200_PUF100</t>
+  </si>
+  <si>
+    <t>RC200_EPS5</t>
+  </si>
+  <si>
+    <t>RC200_EPS10</t>
+  </si>
+  <si>
+    <t>RC200_EPS15</t>
+  </si>
+  <si>
+    <t>RC200_EPS20</t>
+  </si>
+  <si>
+    <t>RC200_EPS25</t>
+  </si>
+  <si>
+    <t>RC200_EPS50</t>
+  </si>
+  <si>
+    <t>RC200_EPS75</t>
+  </si>
+  <si>
     <t>Wall-Name</t>
-  </si>
-  <si>
-    <t>SBB230</t>
-  </si>
-  <si>
-    <t>SBB230_XPS_5</t>
-  </si>
-  <si>
-    <t>SBB230_XPS_10</t>
-  </si>
-  <si>
-    <t>SBB230_XPS_25</t>
-  </si>
-  <si>
-    <t>SBB230_XPS_50</t>
-  </si>
-  <si>
-    <t>ACC200</t>
-  </si>
-  <si>
-    <t>ACC200_EPS_25</t>
-  </si>
-  <si>
-    <t>ACC200_EPS_50</t>
-  </si>
-  <si>
-    <t>ACC200_PUF_50</t>
-  </si>
-  <si>
-    <t>FAB230_PUF_25</t>
-  </si>
-  <si>
-    <t>FAB230_PUF_50</t>
-  </si>
-  <si>
-    <t>SCB200</t>
-  </si>
-  <si>
-    <t>SCB200_XPS_5</t>
-  </si>
-  <si>
-    <t>SCB200_EPS_15</t>
-  </si>
-  <si>
-    <t>SCB200_EPS_20</t>
-  </si>
-  <si>
-    <t>SCB200_XPS_25</t>
-  </si>
-  <si>
-    <t>SCB200_XPS_50</t>
-  </si>
-  <si>
-    <t>SCB200_EPS_25</t>
-  </si>
-  <si>
-    <t>SCB200_EPS_50</t>
-  </si>
-  <si>
-    <t>RC200</t>
-  </si>
-  <si>
-    <t>Roof-Name</t>
-  </si>
-  <si>
-    <t>ML_RC200_XPS25</t>
-  </si>
-  <si>
-    <t>ML_RC200_XPS50</t>
-  </si>
-  <si>
-    <t>RC200_XPS25</t>
-  </si>
-  <si>
-    <t>RC200_XPS50</t>
-  </si>
-  <si>
-    <t>ML_RC200_XPS75</t>
-  </si>
-  <si>
-    <t>ML_RC200_XPS100</t>
-  </si>
-  <si>
-    <t>ML_RC200_PUF25</t>
-  </si>
-  <si>
-    <t>ML_RC200_PUF50</t>
-  </si>
-  <si>
-    <t>ML_RC200_PUF75</t>
-  </si>
-  <si>
-    <t>ML_RC200_PUF100</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS2.5</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS5</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS7.5</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS10</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS12.5</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS15</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS17.5</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS20</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS25</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS50</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS75</t>
-  </si>
-  <si>
-    <t>ML_RC200_EPS100</t>
-  </si>
-  <si>
-    <t>RC200_XPS75</t>
-  </si>
-  <si>
-    <t>RC200_XPS100</t>
-  </si>
-  <si>
-    <t>RC200_PUF25</t>
-  </si>
-  <si>
-    <t>RC200_PUF50</t>
-  </si>
-  <si>
-    <t>RC200_PUF75</t>
-  </si>
-  <si>
-    <t>RC200_PUF100</t>
-  </si>
-  <si>
-    <t>RC200_EPS2.5</t>
-  </si>
-  <si>
-    <t>RC200_EPS5</t>
-  </si>
-  <si>
-    <t>RC200_EPS7.5</t>
-  </si>
-  <si>
-    <t>RC200_EPS10</t>
-  </si>
-  <si>
-    <t>RC200_EPS12.5</t>
-  </si>
-  <si>
-    <t>RC200_EPS15</t>
-  </si>
-  <si>
-    <t>RC200_EPS17.5</t>
-  </si>
-  <si>
-    <t>RC200_EPS20</t>
-  </si>
-  <si>
-    <t>RC200_EPS25</t>
-  </si>
-  <si>
-    <t>RC200_EPS50</t>
-  </si>
-  <si>
-    <t>RC200_EPS75</t>
-  </si>
-  <si>
-    <t>RC200_EPS100</t>
   </si>
   <si>
     <t>Glass-Types</t>
@@ -4048,7 +3871,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4064,6 +3887,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8427"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4121,7 +3950,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4149,21 +3978,19 @@
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="15">
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4320,24 +4147,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D0B1C4E7-375E-428E-A5E9-E1083194D512}" name="CostDB" displayName="CostDB" ref="A1:F20" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D0B1C4E7-375E-428E-A5E9-E1083194D512}" name="CostDB" displayName="CostDB" ref="A1:F20" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:F20" xr:uid="{D0B1C4E7-375E-428E-A5E9-E1083194D512}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7AB808BB-ED43-466A-80D6-AEFF15EA521A}" name="Material" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{5000B84A-F0AE-4B85-AB3D-E13EB1E11392}" name="Cost" dataDxfId="12" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{2B8EB297-2021-4612-9273-022A7F0BEA94}" name="Unit" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{A0D3802B-2C8C-4A18-8970-D383A670E786}" name="Cost (per m2 for unit thickness)" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{7AB808BB-ED43-466A-80D6-AEFF15EA521A}" name="Material" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{5000B84A-F0AE-4B85-AB3D-E13EB1E11392}" name="Cost" dataDxfId="11" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{2B8EB297-2021-4612-9273-022A7F0BEA94}" name="Unit" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{A0D3802B-2C8C-4A18-8970-D383A670E786}" name="Cost (per m2 for unit thickness)" dataDxfId="9">
       <calculatedColumnFormula>B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{781C6105-6CBC-4496-97F2-F3B85651C231}" name="Fixed Cost/m2" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{1D676315-1930-4AA8-982E-7434F4268443}" name="Source" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{781C6105-6CBC-4496-97F2-F3B85651C231}" name="Fixed Cost/m2" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{1D676315-1930-4AA8-982E-7434F4268443}" name="Source" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9919ACC9-777A-40E3-B26D-DDAE1858D3CC}" name="WorkingDB" displayName="WorkingDB" ref="A1:L70" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9919ACC9-777A-40E3-B26D-DDAE1858D3CC}" name="WorkingDB" displayName="WorkingDB" ref="A1:L70" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:L70" xr:uid="{9919ACC9-777A-40E3-B26D-DDAE1858D3CC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L40">
     <sortCondition ref="A1:A40"/>
@@ -4352,7 +4179,7 @@
     <tableColumn id="7" xr3:uid="{18F2EF1C-D54D-40A5-B82E-FC925BF0144C}" name="Cost _x000a_(Rs/m2 of Surface Area for 1m thickness)">
       <calculatedColumnFormula>VLOOKUP(WorkingDB[[#This Row],[Material]],CostDB[#Data],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{975AF750-E3AC-4BB7-B7CC-9ABD6A7C482A}" name="Thermal Diffusivity_x000a_(m2/s)" dataDxfId="6">
+    <tableColumn id="8" xr3:uid="{975AF750-E3AC-4BB7-B7CC-9ABD6A7C482A}" name="Thermal Diffusivity_x000a_(m2/s)" dataDxfId="5">
       <calculatedColumnFormula>B2/(D2*C2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{985080FA-E5BA-44B7-B505-26E1B2AA07A4}" name="Effusivity"/>
@@ -4373,20 +4200,20 @@
     <tableColumn id="4" xr3:uid="{BB74D783-B5DC-4AE2-85D5-60A7231996E1}" name="GLASS-CONDUCT"/>
     <tableColumn id="6" xr3:uid="{8759EF74-95D6-4753-99BF-A7DB4DD1B597}" name="VIS-TRANS"/>
     <tableColumn id="5" xr3:uid="{0CF51170-62CE-419D-8E4C-82459E58DAB2}" name="Climate"/>
-    <tableColumn id="8" xr3:uid="{B0A1CC73-DDC9-4F92-876A-67DF0B25D0CE}" name="U-Value(IP)" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{B0A1CC73-DDC9-4F92-876A-67DF0B25D0CE}" name="U-Value(IP)" dataDxfId="4">
       <calculatedColumnFormula>Table76[[#This Row],[U-value (COG)]]/5.67</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6FDD2159-EE42-4E1B-BC9D-A8175C99276F}" name="SHADING-COEF" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{6FDD2159-EE42-4E1B-BC9D-A8175C99276F}" name="SHADING-COEF" dataDxfId="3">
       <calculatedColumnFormula>Table76[[#This Row],[GLASS-CONDUCT]]/0.87</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{A4747B72-B32D-46E0-AE1A-BF46A179B2F9}" name="Glass">
       <calculatedColumnFormula>IF(Table76[[#This Row],[Glass Type]]="Double Glazed","DG","SG")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0790EAAE-3AEB-4334-B47E-D050FCCFCFEA}" name="GLASS-TYPE" dataDxfId="3">
-      <calculatedColumnFormula>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
+    <tableColumn id="11" xr3:uid="{0790EAAE-3AEB-4334-B47E-D050FCCFCFEA}" name="GLASS-TYPE" dataDxfId="2">
+      <calculatedColumnFormula>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{CE52CB8C-40EC-4571-B677-7C72ACBBB22B}" name="Glass-Types" dataDxfId="2">
-      <calculatedColumnFormula>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{F060659C-349A-44C7-A773-83744EDC4A05}" name="Glass-Types">
+      <calculatedColumnFormula>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -9607,8 +9434,8 @@
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
@@ -9627,10 +9454,10 @@
         <v>964</v>
       </c>
       <c r="C1" t="s">
-        <v>1109</v>
+        <v>965</v>
       </c>
       <c r="D1" t="s">
-        <v>965</v>
+        <v>1111</v>
       </c>
       <c r="E1" t="s">
         <v>966</v>
@@ -9734,7 +9561,7 @@
         <v>998</v>
       </c>
       <c r="C2" t="s">
-        <v>1110</v>
+        <v>999</v>
       </c>
       <c r="D2" t="s">
         <v>999</v>
@@ -9811,7 +9638,7 @@
         <v>1003</v>
       </c>
       <c r="C3" t="s">
-        <v>1111</v>
+        <v>1004</v>
       </c>
       <c r="D3" t="s">
         <v>1004</v>
@@ -9888,7 +9715,7 @@
         <v>1007</v>
       </c>
       <c r="C4" t="s">
-        <v>1112</v>
+        <v>1008</v>
       </c>
       <c r="D4" t="s">
         <v>1008</v>
@@ -9965,7 +9792,7 @@
         <v>1010</v>
       </c>
       <c r="C5" t="s">
-        <v>1113</v>
+        <v>1011</v>
       </c>
       <c r="D5" t="s">
         <v>1011</v>
@@ -10042,7 +9869,7 @@
         <v>1014</v>
       </c>
       <c r="C6" t="s">
-        <v>1114</v>
+        <v>1015</v>
       </c>
       <c r="D6" t="s">
         <v>1015</v>
@@ -10119,7 +9946,7 @@
         <v>1017</v>
       </c>
       <c r="C7" t="s">
-        <v>1115</v>
+        <v>1018</v>
       </c>
       <c r="D7" t="s">
         <v>1018</v>
@@ -10196,7 +10023,7 @@
         <v>1021</v>
       </c>
       <c r="C8" t="s">
-        <v>1116</v>
+        <v>1022</v>
       </c>
       <c r="D8" t="s">
         <v>1022</v>
@@ -10273,7 +10100,7 @@
         <v>1024</v>
       </c>
       <c r="C9" t="s">
-        <v>1117</v>
+        <v>1025</v>
       </c>
       <c r="D9" t="s">
         <v>1025</v>
@@ -10350,7 +10177,7 @@
         <v>1027</v>
       </c>
       <c r="C10" t="s">
-        <v>1118</v>
+        <v>1028</v>
       </c>
       <c r="D10" t="s">
         <v>1028</v>
@@ -10427,7 +10254,7 @@
         <v>1031</v>
       </c>
       <c r="C11" t="s">
-        <v>1119</v>
+        <v>1032</v>
       </c>
       <c r="D11" t="s">
         <v>1032</v>
@@ -10504,7 +10331,7 @@
         <v>1035</v>
       </c>
       <c r="C12" t="s">
-        <v>1120</v>
+        <v>1036</v>
       </c>
       <c r="D12" t="s">
         <v>1036</v>
@@ -10581,7 +10408,7 @@
         <v>1038</v>
       </c>
       <c r="C13" t="s">
-        <v>1121</v>
+        <v>1039</v>
       </c>
       <c r="D13" t="s">
         <v>1039</v>
@@ -10658,7 +10485,7 @@
         <v>1042</v>
       </c>
       <c r="C14" t="s">
-        <v>1122</v>
+        <v>1043</v>
       </c>
       <c r="D14" t="s">
         <v>1043</v>
@@ -10735,7 +10562,7 @@
         <v>1045</v>
       </c>
       <c r="C15" t="s">
-        <v>1123</v>
+        <v>1046</v>
       </c>
       <c r="D15" t="s">
         <v>1046</v>
@@ -10812,7 +10639,7 @@
         <v>1048</v>
       </c>
       <c r="C16" t="s">
-        <v>1124</v>
+        <v>1049</v>
       </c>
       <c r="D16" t="s">
         <v>1049</v>
@@ -10889,7 +10716,7 @@
         <v>1051</v>
       </c>
       <c r="C17" t="s">
-        <v>1125</v>
+        <v>1052</v>
       </c>
       <c r="D17" t="s">
         <v>1052</v>
@@ -10966,7 +10793,7 @@
         <v>1054</v>
       </c>
       <c r="C18" t="s">
-        <v>1126</v>
+        <v>1055</v>
       </c>
       <c r="D18" t="s">
         <v>1055</v>
@@ -11043,7 +10870,7 @@
         <v>1057</v>
       </c>
       <c r="C19" t="s">
-        <v>1127</v>
+        <v>1058</v>
       </c>
       <c r="D19" t="s">
         <v>1058</v>
@@ -11120,7 +10947,7 @@
         <v>1060</v>
       </c>
       <c r="C20" t="s">
-        <v>1128</v>
+        <v>1061</v>
       </c>
       <c r="D20" t="s">
         <v>1061</v>
@@ -11197,7 +11024,7 @@
         <v>1063</v>
       </c>
       <c r="C21" t="s">
-        <v>1129</v>
+        <v>1064</v>
       </c>
       <c r="D21" t="s">
         <v>1064</v>
@@ -11276,13 +11103,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889CC4FE-153F-450B-8B96-60EE246EB7D1}">
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
@@ -11301,10 +11128,10 @@
         <v>964</v>
       </c>
       <c r="C1" t="s">
-        <v>1130</v>
+        <v>965</v>
       </c>
       <c r="D1" t="s">
-        <v>965</v>
+        <v>1089</v>
       </c>
       <c r="E1" t="s">
         <v>966</v>
@@ -11402,26 +11229,27 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1063</v>
       </c>
       <c r="C2" t="s">
-        <v>1129</v>
+        <v>1064</v>
       </c>
       <c r="D2" t="s">
-        <v>1064</v>
+        <v>1100</v>
       </c>
       <c r="E2" t="s">
         <v>1000</v>
       </c>
       <c r="F2" t="s">
-        <v>1107</v>
+        <v>1087</v>
       </c>
       <c r="G2" t="s">
         <v>1065</v>
       </c>
+      <c r="H2" s="23"/>
       <c r="K2" s="17">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
@@ -11459,7 +11287,7 @@
         <v>142.835174768</v>
       </c>
       <c r="AB2" s="21" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="AC2" s="4">
         <f>840* 0.000239005736</f>
@@ -11479,32 +11307,33 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>1066</v>
       </c>
       <c r="C3" t="s">
-        <v>1133</v>
+        <v>1092</v>
       </c>
       <c r="D3" t="s">
-        <v>1131</v>
+        <v>1101</v>
       </c>
       <c r="E3" t="s">
         <v>1000</v>
       </c>
       <c r="F3" t="s">
-        <v>1107</v>
+        <v>1087</v>
       </c>
       <c r="G3" t="s">
-        <v>1108</v>
-      </c>
+        <v>1029</v>
+      </c>
+      <c r="H3" s="3"/>
       <c r="K3" s="4">
-        <f>CONVERT(20,"mm","ft")</f>
+        <f t="shared" ref="K3:K12" si="0">CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="L3" s="17">
-        <f t="shared" ref="L3:L22" si="0">CONVERT(80,"mm","ft")</f>
+        <f t="shared" ref="L3:L12" si="1">CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
       <c r="M3" s="4">
@@ -11512,43 +11341,43 @@
         <v>9.8425196850393706E-2</v>
       </c>
       <c r="Q3" s="4">
-        <f t="shared" ref="Q3:Q22" si="1">0.72*5.678263243</f>
+        <f t="shared" ref="Q3:Q12" si="2">0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
       <c r="R3" s="4">
-        <f t="shared" ref="R3:R22" si="2">0.8*5.678263243</f>
+        <f t="shared" ref="R3:R12" si="3">0.8*5.678263243</f>
         <v>4.5426105944000001</v>
       </c>
       <c r="S3" s="4">
-        <f>0.03*5.678263243</f>
+        <f t="shared" ref="S3:S5" si="4">0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
       <c r="W3" s="4">
-        <f t="shared" ref="W3:W22" si="3">1762*0.062427961</f>
+        <f t="shared" ref="W3:W12" si="5">1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
       <c r="X3" s="4">
-        <f t="shared" ref="X3:X22" si="4">1892*0.062427961</f>
+        <f t="shared" ref="X3:X12" si="6">1892*0.062427961</f>
         <v>118.11370221199999</v>
       </c>
       <c r="Y3" s="4">
-        <f>35*0.062427961</f>
-        <v>2.1849786349999998</v>
+        <f>40*0.062427961</f>
+        <v>2.4971184399999999</v>
       </c>
       <c r="AB3" s="22" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="AC3" s="4">
-        <f t="shared" ref="AC3:AC22" si="5">840* 0.000239005736</f>
+        <f t="shared" ref="AC3:AC12" si="7">840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
       <c r="AD3" s="18">
-        <f t="shared" ref="AD3:AD22" si="6">880* 0.000239005736</f>
+        <f t="shared" ref="AD3:AD12" si="8">880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
       <c r="AE3" s="4">
-        <f>1213* 0.000239005736</f>
-        <v>0.289913957768</v>
+        <f>1590* 0.000239005736</f>
+        <v>0.38001912024000001</v>
       </c>
       <c r="AI3">
         <v>1</v>
@@ -11556,691 +11385,696 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>1067</v>
       </c>
       <c r="C4" t="s">
-        <v>1134</v>
+        <v>1090</v>
       </c>
       <c r="D4" t="s">
-        <v>1132</v>
+        <v>1102</v>
       </c>
       <c r="E4" t="s">
         <v>1000</v>
       </c>
       <c r="F4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L4" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M4" s="4">
+        <f>CONVERT(80,"mm","ft")</f>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R4" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S4" s="4">
+        <f t="shared" si="4"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="W4" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" ref="Y4:Y5" si="9">40*0.062427961</f>
+        <v>2.4971184399999999</v>
+      </c>
+      <c r="AB4" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AC4" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD4" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE4" s="4">
+        <f t="shared" ref="AE4:AE5" si="10">1590* 0.000239005736</f>
+        <v>0.38001912024000001</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="K5" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L5" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M5" s="4">
+        <f>CONVERT(100,"mm","ft")</f>
+        <v>0.32808398950131235</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S5" s="4">
+        <f t="shared" si="4"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="W5" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X5" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y5" s="4">
+        <f t="shared" si="9"/>
+        <v>2.4971184399999999</v>
+      </c>
+      <c r="AB5" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AC5" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD5" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE5" s="4">
+        <f t="shared" si="10"/>
+        <v>0.38001912024000001</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L6" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M6" s="4">
+        <f>CONVERT(10,"mm","ft")</f>
+        <v>3.2808398950131233E-2</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S6" s="4">
+        <f t="shared" ref="S6:S12" si="11">0.04*5.678263243</f>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W6" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" ref="Y6:Y12" si="12">28*0.062427961</f>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB6" s="22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AC6" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD6" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE6" s="4">
+        <f t="shared" ref="AE6:AE12" si="13">1213* 0.000239005736</f>
+        <v>0.289913957768</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="K7" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L7" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M7" s="4">
+        <f t="shared" ref="M7" si="14">CONVERT(10,"mm","ft")</f>
+        <v>3.2808398950131233E-2</v>
+      </c>
+      <c r="Q7" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R7" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S7" s="4">
+        <f t="shared" si="11"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W7" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X7" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y7" s="4">
+        <f t="shared" si="12"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB7" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AC7" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD7" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE7" s="4">
+        <f t="shared" si="13"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="K8" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L8" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" ref="M8:M9" si="15">CONVERT(20,"mm","ft")</f>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R8" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S8" s="4">
+        <f t="shared" si="11"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W8" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X8" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y8" s="4">
+        <f t="shared" si="12"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB8" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AC8" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD8" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE8" s="4">
+        <f t="shared" si="13"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D9" t="s">
         <v>1107</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="K9" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L9" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="15"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R9" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S9" s="4">
+        <f t="shared" si="11"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W9" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X9" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y9" s="4">
+        <f t="shared" si="12"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB9" s="22" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AC9" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD9" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE9" s="4">
+        <f t="shared" si="13"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D10" t="s">
         <v>1108</v>
       </c>
-      <c r="K4" s="4">
-        <f t="shared" ref="K4:K22" si="7">CONVERT(20,"mm","ft")</f>
+      <c r="E10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="0"/>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L10" s="17">
+        <f t="shared" si="1"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="M10" s="4">
+        <f>CONVERT(30,"mm","ft")</f>
+        <v>9.8425196850393706E-2</v>
+      </c>
+      <c r="Q10" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R10" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S10" s="4">
+        <f t="shared" si="11"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W10" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X10" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y10" s="4">
+        <f t="shared" si="12"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB10" s="22" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AC10" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD10" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE10" s="4">
+        <f t="shared" si="13"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L11" s="17">
+        <f t="shared" si="1"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M11" s="4">
         <f>CONVERT(50,"mm","ft")</f>
         <v>0.16404199475065617</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q11" s="4">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="R11" s="4">
+        <f t="shared" si="3"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="S11" s="4">
+        <f t="shared" si="11"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W11" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X11" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y11" s="4">
+        <f t="shared" si="12"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB11" s="22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AC11" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD11" s="18">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="AE11" s="4">
+        <f t="shared" si="13"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K12" s="4">
+        <f t="shared" si="0"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="L12" s="17">
         <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R4" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S4" s="4">
-        <f t="shared" ref="S4:S10" si="8">0.03*5.678263243</f>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W4" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X4" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y4" s="4">
-        <f t="shared" ref="Y4:Y6" si="9">35*0.062427961</f>
-        <v>2.1849786349999998</v>
-      </c>
-      <c r="AB4" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="AC4" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD4" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE4" s="4">
-        <f t="shared" ref="AE4:AE6" si="10">1213* 0.000239005736</f>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K5" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L5" s="17">
-        <f t="shared" si="0"/>
         <v>0.26246719160104987</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M12" s="4">
         <f>CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
-      <c r="Q5" s="4">
-        <f t="shared" si="1"/>
+      <c r="Q12" s="4">
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
-      <c r="R5" s="4">
-        <f t="shared" si="2"/>
+      <c r="R12" s="4">
+        <f t="shared" si="3"/>
         <v>4.5426105944000001</v>
       </c>
-      <c r="S5" s="4">
+      <c r="S12" s="4">
+        <f t="shared" si="11"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="W12" s="4">
+        <f t="shared" si="5"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="X12" s="4">
+        <f t="shared" si="6"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="Y12" s="4">
+        <f t="shared" si="12"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="AB12" s="22" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AC12" s="4">
+        <f t="shared" si="7"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="AD12" s="18">
         <f t="shared" si="8"/>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W5" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X5" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y5" s="4">
-        <f t="shared" si="9"/>
-        <v>2.1849786349999998</v>
-      </c>
-      <c r="AB5" s="22" t="s">
-        <v>1089</v>
-      </c>
-      <c r="AC5" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD5" s="18">
-        <f t="shared" si="6"/>
         <v>0.21032504767999999</v>
       </c>
-      <c r="AE5" s="4">
-        <f t="shared" si="10"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1136</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K6" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L6" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M6" s="4">
-        <f>CONVERT(100,"mm","ft")</f>
-        <v>0.32808398950131235</v>
-      </c>
-      <c r="Q6" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R6" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S6" s="4">
-        <f t="shared" si="8"/>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W6" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X6" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y6" s="4">
-        <f t="shared" si="9"/>
-        <v>2.1849786349999998</v>
-      </c>
-      <c r="AB6" s="22" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AC6" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD6" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE6" s="4">
-        <f t="shared" si="10"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K7" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L7" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M7" s="4">
-        <f>CONVERT(30,"mm","ft")</f>
-        <v>9.8425196850393706E-2</v>
-      </c>
-      <c r="Q7" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R7" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S7" s="4">
-        <f t="shared" si="8"/>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W7" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X7" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y7" s="4">
-        <f>40*0.062427961</f>
-        <v>2.4971184399999999</v>
-      </c>
-      <c r="AB7" s="22" t="s">
-        <v>1091</v>
-      </c>
-      <c r="AC7" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD7" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE7" s="4">
-        <f>1590* 0.000239005736</f>
-        <v>0.38001912024000001</v>
-      </c>
-      <c r="AI7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
-        <v>1092</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1156</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K8" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L8" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M8" s="4">
-        <f>CONVERT(50,"mm","ft")</f>
-        <v>0.16404199475065617</v>
-      </c>
-      <c r="Q8" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R8" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S8" s="4">
-        <f t="shared" si="8"/>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W8" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X8" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y8" s="4">
-        <f t="shared" ref="Y8:Y10" si="11">40*0.062427961</f>
-        <v>2.4971184399999999</v>
-      </c>
-      <c r="AB8" s="22" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AC8" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD8" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE8" s="4">
-        <f t="shared" ref="AE8:AE10" si="12">1590* 0.000239005736</f>
-        <v>0.38001912024000001</v>
-      </c>
-      <c r="AI8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K9" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L9" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M9" s="4">
-        <f>CONVERT(80,"mm","ft")</f>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="Q9" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R9" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S9" s="4">
-        <f t="shared" si="8"/>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W9" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X9" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y9" s="4">
-        <f t="shared" si="11"/>
-        <v>2.4971184399999999</v>
-      </c>
-      <c r="AB9" s="22" t="s">
-        <v>1093</v>
-      </c>
-      <c r="AC9" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD9" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE9" s="4">
-        <f t="shared" si="12"/>
-        <v>0.38001912024000001</v>
-      </c>
-      <c r="AI9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K10" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L10" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M10" s="4">
-        <f>CONVERT(100,"mm","ft")</f>
-        <v>0.32808398950131235</v>
-      </c>
-      <c r="Q10" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R10" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S10" s="4">
-        <f t="shared" si="8"/>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="W10" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X10" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y10" s="4">
-        <f t="shared" si="11"/>
-        <v>2.4971184399999999</v>
-      </c>
-      <c r="AB10" s="22" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AC10" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD10" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE10" s="4">
-        <f t="shared" si="12"/>
-        <v>0.38001912024000001</v>
-      </c>
-      <c r="AI10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K11" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L11" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M11" s="4">
-        <f>CONVERT(0,"mm","ft")</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R11" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S11" s="4">
-        <f>0.04*5.678263243</f>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W11" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X11" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y11" s="4">
-        <f>28*0.062427961</f>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB11" s="22" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AC11" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD11" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE11" s="4">
-        <f>1213* 0.000239005736</f>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1142</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K12" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L12" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M12" s="4">
-        <f>CONVERT(10,"mm","ft")</f>
-        <v>3.2808398950131233E-2</v>
-      </c>
-      <c r="Q12" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R12" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S12" s="4">
-        <f t="shared" ref="S12:S22" si="13">0.04*5.678263243</f>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W12" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X12" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y12" s="4">
-        <f t="shared" ref="Y12:Y22" si="14">28*0.062427961</f>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB12" s="22" t="s">
-        <v>1096</v>
-      </c>
-      <c r="AC12" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD12" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
       <c r="AE12" s="4">
-        <f t="shared" ref="AE12:AE22" si="15">1213* 0.000239005736</f>
+        <f t="shared" si="13"/>
         <v>0.289913957768</v>
       </c>
       <c r="AI12">
@@ -12248,777 +12082,7 @@
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K13" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M13" s="4">
-        <f t="shared" ref="M13:M15" si="16">CONVERT(10,"mm","ft")</f>
-        <v>3.2808398950131233E-2</v>
-      </c>
-      <c r="Q13" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R13" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S13" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W13" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X13" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y13" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB13" s="22" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AC13" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD13" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE13" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K14" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L14" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="16"/>
-        <v>3.2808398950131233E-2</v>
-      </c>
-      <c r="Q14" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R14" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S14" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W14" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X14" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y14" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB14" s="22" t="s">
-        <v>1098</v>
-      </c>
-      <c r="AC14" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD14" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE14" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K15" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L15" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M15" s="4">
-        <f t="shared" si="16"/>
-        <v>3.2808398950131233E-2</v>
-      </c>
-      <c r="Q15" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R15" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S15" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W15" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X15" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y15" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB15" s="22" t="s">
-        <v>1099</v>
-      </c>
-      <c r="AC15" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD15" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE15" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>1100</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K16" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L16" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M16" s="4">
-        <f t="shared" ref="M16:M18" si="17">CONVERT(20,"mm","ft")</f>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="Q16" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R16" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S16" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W16" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X16" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y16" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB16" s="22" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AC16" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD16" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE16" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1165</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K17" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L17" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M17" s="4">
-        <f t="shared" si="17"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="Q17" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R17" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S17" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W17" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X17" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y17" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB17" s="22" t="s">
-        <v>1101</v>
-      </c>
-      <c r="AC17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD17" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE17" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K18" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L18" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M18" s="4">
-        <f t="shared" si="17"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="Q18" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R18" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S18" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W18" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X18" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y18" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB18" s="22" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AC18" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD18" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE18" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K19" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L19" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M19" s="4">
-        <f>CONVERT(30,"mm","ft")</f>
-        <v>9.8425196850393706E-2</v>
-      </c>
-      <c r="Q19" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R19" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S19" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W19" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X19" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y19" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB19" s="22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AC19" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD19" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE19" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1150</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K20" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L20" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M20" s="4">
-        <f>CONVERT(50,"mm","ft")</f>
-        <v>0.16404199475065617</v>
-      </c>
-      <c r="Q20" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R20" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S20" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W20" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X20" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y20" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB20" s="22" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AC20" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD20" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE20" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K21" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L21" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M21" s="4">
-        <f>CONVERT(80,"mm","ft")</f>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="Q21" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R21" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S21" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W21" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X21" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y21" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB21" s="22" t="s">
-        <v>1105</v>
-      </c>
-      <c r="AC21" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD21" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE21" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1152</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K22" s="4">
-        <f t="shared" si="7"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="L22" s="17">
-        <f t="shared" si="0"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="M22" s="4">
-        <f>CONVERT(100,"mm","ft")</f>
-        <v>0.32808398950131235</v>
-      </c>
-      <c r="Q22" s="4">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="R22" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="S22" s="4">
-        <f t="shared" si="13"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="W22" s="4">
-        <f t="shared" si="3"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="X22" s="4">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="Y22" s="4">
-        <f t="shared" si="14"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="AB22" s="22" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AC22" s="4">
-        <f t="shared" si="5"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="AD22" s="18">
-        <f t="shared" si="6"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="AE22" s="4">
-        <f t="shared" si="15"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="AI22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="L23" s="4"/>
+      <c r="L13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -13039,8 +12103,7 @@
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.77734375" customWidth="1"/>
+    <col min="9" max="10" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -13072,7 +12135,7 @@
         <v>962</v>
       </c>
       <c r="J1" t="s">
-        <v>1171</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -13104,12 +12167,12 @@
         <v>DG</v>
       </c>
       <c r="I2" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.18_0.57_0.4_Cold</v>
       </c>
       <c r="J2" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.18_0.57_0.4_Cold</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -13141,12 +12204,12 @@
         <v>DG</v>
       </c>
       <c r="I3" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.18_0.69_0.4_Cold</v>
       </c>
       <c r="J3" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.18_0.69_0.4_Cold</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -13178,12 +12241,12 @@
         <v>DG</v>
       </c>
       <c r="I4" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.18_0.8_0.4_Cold</v>
       </c>
       <c r="J4" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.18_0.8_0.4_Cold</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -13215,12 +12278,12 @@
         <v>DG</v>
       </c>
       <c r="I5" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.26_0.57_0.4_Cold</v>
       </c>
       <c r="J5" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.26_0.57_0.4_Cold</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -13252,12 +12315,12 @@
         <v>DG</v>
       </c>
       <c r="I6" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.26_0.69_0.4_Cold</v>
       </c>
       <c r="J6" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.26_0.69_0.4_Cold</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -13289,12 +12352,12 @@
         <v>DG</v>
       </c>
       <c r="I7" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.26_0.8_0.4_Cold</v>
       </c>
       <c r="J7" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.26_0.8_0.4_Cold</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -13326,12 +12389,12 @@
         <v>DG</v>
       </c>
       <c r="I8" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.44_0.57_0.4_Cold</v>
       </c>
       <c r="J8" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.44_0.57_0.4_Cold</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -13363,12 +12426,12 @@
         <v>DG</v>
       </c>
       <c r="I9" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.44_0.69_0.4_Cold</v>
       </c>
       <c r="J9" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.44_0.69_0.4_Cold</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -13400,12 +12463,12 @@
         <v>DG</v>
       </c>
       <c r="I10" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.44_0.8_0.4_Cold</v>
       </c>
       <c r="J10" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.44_0.8_0.4_Cold</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -13437,12 +12500,12 @@
         <v>DG</v>
       </c>
       <c r="I11" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.63_0.57_0.4_Cold</v>
       </c>
       <c r="J11" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.63_0.57_0.4_Cold</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -13474,12 +12537,12 @@
         <v>DG</v>
       </c>
       <c r="I12" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.63_0.69_0.4_Cold</v>
       </c>
       <c r="J12" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.63_0.69_0.4_Cold</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -13511,12 +12574,12 @@
         <v>DG</v>
       </c>
       <c r="I13" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.63_0.8_0.4_Cold</v>
       </c>
       <c r="J13" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.63_0.8_0.4_Cold</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -13548,12 +12611,12 @@
         <v>SG</v>
       </c>
       <c r="I14" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.57_0.4_Cold</v>
       </c>
       <c r="J14" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.57_0.4_Cold</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -13585,12 +12648,12 @@
         <v>SG</v>
       </c>
       <c r="I15" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.69_0.4_Cold</v>
       </c>
       <c r="J15" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.69_0.4_Cold</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -13622,12 +12685,12 @@
         <v>SG</v>
       </c>
       <c r="I16" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.8_0.4_Cold</v>
       </c>
       <c r="J16" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.8_0.4_Cold</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -13659,12 +12722,12 @@
         <v>SG</v>
       </c>
       <c r="I17" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.57_0.4_Cold</v>
       </c>
       <c r="J17" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.5_0.57_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.57_0.4_Cold</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -13696,12 +12759,12 @@
         <v>SG</v>
       </c>
       <c r="I18" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.69_0.4_Cold</v>
       </c>
       <c r="J18" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.6_0.69_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.69_0.4_Cold</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -13733,12 +12796,12 @@
         <v>SG</v>
       </c>
       <c r="I19" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.8_0.4_Cold</v>
       </c>
       <c r="J19" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.7_0.8_0.4_Cold</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.8_0.4_Cold</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -13770,12 +12833,12 @@
         <v>SG</v>
       </c>
       <c r="I20" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.67_0.34_0.4_Others</v>
       </c>
       <c r="J20" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.67_0.34_0.4_Others</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -13807,12 +12870,12 @@
         <v>SG</v>
       </c>
       <c r="I21" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.34_0.4_Others</v>
       </c>
       <c r="J21" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.34_0.4_Others</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -13844,12 +12907,12 @@
         <v>SG</v>
       </c>
       <c r="I22" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.4_0.46_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.46_0.4_Others</v>
       </c>
       <c r="J22" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.4_0.46_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.46_0.4_Others</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -13881,12 +12944,12 @@
         <v>SG</v>
       </c>
       <c r="I23" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.5_0.57_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.57_0.4_Others</v>
       </c>
       <c r="J23" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.5_0.57_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.57_0.4_Others</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -13918,12 +12981,12 @@
         <v>SG</v>
       </c>
       <c r="I24" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.6_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.69_0.4_Others</v>
       </c>
       <c r="J24" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.6_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.69_0.4_Others</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -13955,12 +13018,12 @@
         <v>SG</v>
       </c>
       <c r="I25" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.7_0.8_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.8_0.4_Others</v>
       </c>
       <c r="J25" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.7_0.8_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_0.85_0.8_0.4_Others</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -13992,12 +13055,12 @@
         <v>SG</v>
       </c>
       <c r="I26" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.34_0.4_Others</v>
       </c>
       <c r="J26" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.34_0.4_Others</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -14029,12 +13092,12 @@
         <v>SG</v>
       </c>
       <c r="I27" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.4_0.46_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.46_0.4_Others</v>
       </c>
       <c r="J27" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.4_0.46_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.46_0.4_Others</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -14066,12 +13129,12 @@
         <v>SG</v>
       </c>
       <c r="I28" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.5_0.57_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.57_0.4_Others</v>
       </c>
       <c r="J28" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.5_0.57_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.57_0.4_Others</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -14103,12 +13166,12 @@
         <v>SG</v>
       </c>
       <c r="I29" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.6_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.69_0.4_Others</v>
       </c>
       <c r="J29" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.6_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.69_0.4_Others</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -14140,12 +13203,12 @@
         <v>SG</v>
       </c>
       <c r="I30" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_SG_0.7_0.8_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.8_0.4_Others</v>
       </c>
       <c r="J30" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>SG_0.7_0.8_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_SG_1.01_0.8_0.4_Others</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -14177,12 +13240,12 @@
         <v>DG</v>
       </c>
       <c r="I31" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.2_0.23_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.23_0.4_Others</v>
       </c>
       <c r="J31" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.2_0.23_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.23_0.4_Others</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -14214,12 +13277,12 @@
         <v>DG</v>
       </c>
       <c r="I32" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.34_0.4_Others</v>
       </c>
       <c r="J32" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.3_0.34_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.34_0.4_Others</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -14251,12 +13314,12 @@
         <v>DG</v>
       </c>
       <c r="I33" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.4_0.46_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.46_0.4_Others</v>
       </c>
       <c r="J33" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.4_0.46_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.46_0.4_Others</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -14288,12 +13351,12 @@
         <v>DG</v>
       </c>
       <c r="I34" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.5_0.57_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.57_0.4_Others</v>
       </c>
       <c r="J34" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.5_0.57_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.57_0.4_Others</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -14325,12 +13388,12 @@
         <v>DG</v>
       </c>
       <c r="I35" t="str">
-        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>ML_DG_0.6_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.69_0.4_Others</v>
       </c>
       <c r="J35" t="str">
-        <f>CONCATENATE(Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[GLASS-CONDUCT]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
-        <v>DG_0.6_0.69_0.4_Others</v>
+        <f>CONCATENATE("ML_",Table76[[#This Row],[Glass]],"_",ROUND(Table76[[#This Row],[U-Value(IP)]],2),"_",ROUND(Table76[[#This Row],[SHADING-COEF]],2),"_",Table76[[#This Row],[VIS-TRANS]],"_",Table76[[#This Row],[Climate]])</f>
+        <v>ML_DG_0.49_0.69_0.4_Others</v>
       </c>
     </row>
   </sheetData>

--- a/database/ML_ScaleUp_v02.xlsx
+++ b/database/ML_ScaleUp_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\260108AWESIM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6653CEC6-D7D2-4F53-B4AF-191EE6F9D3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD9A9F6-8B44-4BD5-B935-E64B692B7F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="10" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{FC86CB77-5C7F-4BB1-97B0-B96BB59000A5}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialDb-ENS2018" sheetId="1" r:id="rId1"/>
